--- a/data/output/pesquisa_cnpj_resultado.xlsx
+++ b/data/output/pesquisa_cnpj_resultado.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1923" uniqueCount="653">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2028" uniqueCount="662">
   <si>
     <t>nomeAtendente</t>
   </si>
@@ -664,6 +664,321 @@
     <t>VIEIRA SERVICOS DE BUFFET</t>
   </si>
   <si>
+    <t>15280561000169</t>
+  </si>
+  <si>
+    <t>3070546000107</t>
+  </si>
+  <si>
+    <t>64414622000149</t>
+  </si>
+  <si>
+    <t>48562907000170</t>
+  </si>
+  <si>
+    <t>7274690000116</t>
+  </si>
+  <si>
+    <t>55333145000104</t>
+  </si>
+  <si>
+    <t>52261829000141</t>
+  </si>
+  <si>
+    <t>55029745000175</t>
+  </si>
+  <si>
+    <t>29237543000109</t>
+  </si>
+  <si>
+    <t>36601122000180</t>
+  </si>
+  <si>
+    <t>40837487000186</t>
+  </si>
+  <si>
+    <t>64731620000183</t>
+  </si>
+  <si>
+    <t>65391507000169</t>
+  </si>
+  <si>
+    <t>66276608000151</t>
+  </si>
+  <si>
+    <t>41112807000101</t>
+  </si>
+  <si>
+    <t>51307679000105</t>
+  </si>
+  <si>
+    <t>32750806000193</t>
+  </si>
+  <si>
+    <t>54889790000137</t>
+  </si>
+  <si>
+    <t>34699213000175</t>
+  </si>
+  <si>
+    <t>9422273000107</t>
+  </si>
+  <si>
+    <t>13159001000125</t>
+  </si>
+  <si>
+    <t>49313373000101</t>
+  </si>
+  <si>
+    <t>29530344000194</t>
+  </si>
+  <si>
+    <t>63970774000165</t>
+  </si>
+  <si>
+    <t>57013589000180</t>
+  </si>
+  <si>
+    <t>11635824000154</t>
+  </si>
+  <si>
+    <t>64927707000120</t>
+  </si>
+  <si>
+    <t>40050453000147</t>
+  </si>
+  <si>
+    <t>59834120000137</t>
+  </si>
+  <si>
+    <t>12962386000100</t>
+  </si>
+  <si>
+    <t>32484626000107</t>
+  </si>
+  <si>
+    <t>63364739000100</t>
+  </si>
+  <si>
+    <t>60394938000165</t>
+  </si>
+  <si>
+    <t>54448012000102</t>
+  </si>
+  <si>
+    <t>59209988000146</t>
+  </si>
+  <si>
+    <t>39288435000119</t>
+  </si>
+  <si>
+    <t>17397084000141</t>
+  </si>
+  <si>
+    <t>37018349000160</t>
+  </si>
+  <si>
+    <t>17784817000109</t>
+  </si>
+  <si>
+    <t>50277820000101</t>
+  </si>
+  <si>
+    <t>24296850000147</t>
+  </si>
+  <si>
+    <t>52311623000189</t>
+  </si>
+  <si>
+    <t>19970932000195</t>
+  </si>
+  <si>
+    <t>17473809000133</t>
+  </si>
+  <si>
+    <t>64620869000111</t>
+  </si>
+  <si>
+    <t>19317140000116</t>
+  </si>
+  <si>
+    <t>47144853000160</t>
+  </si>
+  <si>
+    <t>18530119000131</t>
+  </si>
+  <si>
+    <t>34360182000123</t>
+  </si>
+  <si>
+    <t>59137961000195</t>
+  </si>
+  <si>
+    <t>14784541000162</t>
+  </si>
+  <si>
+    <t>44047970000118</t>
+  </si>
+  <si>
+    <t>60962378000106</t>
+  </si>
+  <si>
+    <t>18746186000198</t>
+  </si>
+  <si>
+    <t>29696014000173</t>
+  </si>
+  <si>
+    <t>34822047000152</t>
+  </si>
+  <si>
+    <t>52052110000109</t>
+  </si>
+  <si>
+    <t>51227599000131</t>
+  </si>
+  <si>
+    <t>33853038000166</t>
+  </si>
+  <si>
+    <t>23248210000107</t>
+  </si>
+  <si>
+    <t>30814593000190</t>
+  </si>
+  <si>
+    <t>42438349000150</t>
+  </si>
+  <si>
+    <t>19918377000152</t>
+  </si>
+  <si>
+    <t>4545089000122</t>
+  </si>
+  <si>
+    <t>39799505000101</t>
+  </si>
+  <si>
+    <t>31191129000158</t>
+  </si>
+  <si>
+    <t>33233308000136</t>
+  </si>
+  <si>
+    <t>7216822000668</t>
+  </si>
+  <si>
+    <t>35714405000176</t>
+  </si>
+  <si>
+    <t>33037883000163</t>
+  </si>
+  <si>
+    <t>4419014000103</t>
+  </si>
+  <si>
+    <t>19738868000111</t>
+  </si>
+  <si>
+    <t>57188334000158</t>
+  </si>
+  <si>
+    <t>34454171000102</t>
+  </si>
+  <si>
+    <t>33016895000101</t>
+  </si>
+  <si>
+    <t>65731411000100</t>
+  </si>
+  <si>
+    <t>55406246000150</t>
+  </si>
+  <si>
+    <t>7588961000108</t>
+  </si>
+  <si>
+    <t>22742301000123</t>
+  </si>
+  <si>
+    <t>9415536000142</t>
+  </si>
+  <si>
+    <t>64633565000199</t>
+  </si>
+  <si>
+    <t>13744159000162</t>
+  </si>
+  <si>
+    <t>12332167000139</t>
+  </si>
+  <si>
+    <t>19509749000197</t>
+  </si>
+  <si>
+    <t>61971120000120</t>
+  </si>
+  <si>
+    <t>12643470000152</t>
+  </si>
+  <si>
+    <t>62734248000133</t>
+  </si>
+  <si>
+    <t>27458857000106</t>
+  </si>
+  <si>
+    <t>58967474000197</t>
+  </si>
+  <si>
+    <t>53637045000138</t>
+  </si>
+  <si>
+    <t>66155958000160</t>
+  </si>
+  <si>
+    <t>56894834000142</t>
+  </si>
+  <si>
+    <t>48856493000192</t>
+  </si>
+  <si>
+    <t>62540238000167</t>
+  </si>
+  <si>
+    <t>19018026000195</t>
+  </si>
+  <si>
+    <t>14415275000109</t>
+  </si>
+  <si>
+    <t>30111864000141</t>
+  </si>
+  <si>
+    <t>39861087000127</t>
+  </si>
+  <si>
+    <t>882726000103</t>
+  </si>
+  <si>
+    <t>40240878000119</t>
+  </si>
+  <si>
+    <t>24344687000140</t>
+  </si>
+  <si>
+    <t>10625190000196</t>
+  </si>
+  <si>
+    <t>37016656000102</t>
+  </si>
+  <si>
+    <t>30348035000187</t>
+  </si>
+  <si>
+    <t>18053359000192</t>
+  </si>
+  <si>
     <t>CAPUAVA</t>
   </si>
   <si>
@@ -967,319 +1282,31 @@
     <t>Olá!Dando continuidade ao atendimento realizado pelo Sebrae, seguem algumas orientações importantes:Acesse o site do Sebrae Goiás — www.sebraego.com.br — e conheça tudo o que o Sebrae tem para apoiar o crescimento da sua empresa.Conforme conversamos, aproveite os materiais digitais do Sebrae, especialmente os e-books e vídeos desenvolvidos para o atendimento do Sebrae na sua Empresa.Ah, e não se esqueça de responder o e-mail NPS, de avaliação da minha visita. Sua opinião é essencial para que o Sebrae continue aprimorando seus atendimentos.O Sebrae está sempre à disposição das Micro e Pequenas Empresas pelo site www.sebraego.com.br e pelo 0800 570 0800.Obrigado e até breve!</t>
   </si>
   <si>
-    <t>15280561000169</t>
-  </si>
-  <si>
     <t>03070546000107</t>
   </si>
   <si>
-    <t>64414622000149</t>
-  </si>
-  <si>
-    <t>48562907000170</t>
-  </si>
-  <si>
     <t>07274690000116</t>
   </si>
   <si>
-    <t>55333145000104</t>
-  </si>
-  <si>
-    <t>52261829000141</t>
-  </si>
-  <si>
-    <t>55029745000175</t>
-  </si>
-  <si>
-    <t>29237543000109</t>
-  </si>
-  <si>
-    <t>36601122000180</t>
-  </si>
-  <si>
-    <t>40837487000186</t>
-  </si>
-  <si>
-    <t>64731620000183</t>
-  </si>
-  <si>
-    <t>65391507000169</t>
-  </si>
-  <si>
-    <t>66276608000151</t>
-  </si>
-  <si>
-    <t>41112807000101</t>
-  </si>
-  <si>
-    <t>51307679000105</t>
-  </si>
-  <si>
-    <t>32750806000193</t>
-  </si>
-  <si>
-    <t>54889790000137</t>
-  </si>
-  <si>
-    <t>34699213000175</t>
-  </si>
-  <si>
     <t>09422273000107</t>
   </si>
   <si>
-    <t>13159001000125</t>
-  </si>
-  <si>
-    <t>49313373000101</t>
-  </si>
-  <si>
-    <t>29530344000194</t>
-  </si>
-  <si>
-    <t>63970774000165</t>
-  </si>
-  <si>
-    <t>57013589000180</t>
-  </si>
-  <si>
-    <t>11635824000154</t>
-  </si>
-  <si>
-    <t>64927707000120</t>
-  </si>
-  <si>
-    <t>40050453000147</t>
-  </si>
-  <si>
-    <t>59834120000137</t>
-  </si>
-  <si>
-    <t>12962386000100</t>
-  </si>
-  <si>
-    <t>32484626000107</t>
-  </si>
-  <si>
-    <t>63364739000100</t>
-  </si>
-  <si>
-    <t>60394938000165</t>
-  </si>
-  <si>
-    <t>54448012000102</t>
-  </si>
-  <si>
-    <t>59209988000146</t>
-  </si>
-  <si>
-    <t>39288435000119</t>
-  </si>
-  <si>
-    <t>17397084000141</t>
-  </si>
-  <si>
-    <t>37018349000160</t>
-  </si>
-  <si>
-    <t>17784817000109</t>
-  </si>
-  <si>
-    <t>50277820000101</t>
-  </si>
-  <si>
-    <t>24296850000147</t>
-  </si>
-  <si>
-    <t>52311623000189</t>
-  </si>
-  <si>
-    <t>19970932000195</t>
-  </si>
-  <si>
-    <t>17473809000133</t>
-  </si>
-  <si>
-    <t>64620869000111</t>
-  </si>
-  <si>
-    <t>19317140000116</t>
-  </si>
-  <si>
-    <t>47144853000160</t>
-  </si>
-  <si>
-    <t>18530119000131</t>
-  </si>
-  <si>
-    <t>34360182000123</t>
-  </si>
-  <si>
-    <t>59137961000195</t>
-  </si>
-  <si>
-    <t>14784541000162</t>
-  </si>
-  <si>
-    <t>44047970000118</t>
-  </si>
-  <si>
-    <t>60962378000106</t>
-  </si>
-  <si>
-    <t>18746186000198</t>
-  </si>
-  <si>
-    <t>29696014000173</t>
-  </si>
-  <si>
-    <t>34822047000152</t>
-  </si>
-  <si>
-    <t>52052110000109</t>
-  </si>
-  <si>
-    <t>51227599000131</t>
-  </si>
-  <si>
-    <t>33853038000166</t>
-  </si>
-  <si>
-    <t>23248210000107</t>
-  </si>
-  <si>
-    <t>30814593000190</t>
-  </si>
-  <si>
-    <t>42438349000150</t>
-  </si>
-  <si>
-    <t>19918377000152</t>
-  </si>
-  <si>
     <t>04545089000122</t>
   </si>
   <si>
-    <t>39799505000101</t>
-  </si>
-  <si>
-    <t>31191129000158</t>
-  </si>
-  <si>
-    <t>33233308000136</t>
-  </si>
-  <si>
     <t>07216822000668</t>
   </si>
   <si>
-    <t>35714405000176</t>
-  </si>
-  <si>
-    <t>33037883000163</t>
-  </si>
-  <si>
     <t>04419014000103</t>
   </si>
   <si>
-    <t>19738868000111</t>
-  </si>
-  <si>
-    <t>57188334000158</t>
-  </si>
-  <si>
-    <t>34454171000102</t>
-  </si>
-  <si>
-    <t>33016895000101</t>
-  </si>
-  <si>
-    <t>65731411000100</t>
-  </si>
-  <si>
-    <t>55406246000150</t>
-  </si>
-  <si>
     <t>07588961000108</t>
   </si>
   <si>
-    <t>22742301000123</t>
-  </si>
-  <si>
     <t>09415536000142</t>
   </si>
   <si>
-    <t>64633565000199</t>
-  </si>
-  <si>
-    <t>13744159000162</t>
-  </si>
-  <si>
-    <t>12332167000139</t>
-  </si>
-  <si>
-    <t>19509749000197</t>
-  </si>
-  <si>
-    <t>61971120000120</t>
-  </si>
-  <si>
-    <t>12643470000152</t>
-  </si>
-  <si>
-    <t>62734248000133</t>
-  </si>
-  <si>
-    <t>27458857000106</t>
-  </si>
-  <si>
-    <t>58967474000197</t>
-  </si>
-  <si>
-    <t>53637045000138</t>
-  </si>
-  <si>
-    <t>66155958000160</t>
-  </si>
-  <si>
-    <t>56894834000142</t>
-  </si>
-  <si>
-    <t>48856493000192</t>
-  </si>
-  <si>
-    <t>62540238000167</t>
-  </si>
-  <si>
-    <t>19018026000195</t>
-  </si>
-  <si>
-    <t>14415275000109</t>
-  </si>
-  <si>
-    <t>30111864000141</t>
-  </si>
-  <si>
-    <t>39861087000127</t>
-  </si>
-  <si>
     <t>00882726000103</t>
-  </si>
-  <si>
-    <t>40240878000119</t>
-  </si>
-  <si>
-    <t>24344687000140</t>
-  </si>
-  <si>
-    <t>10625190000196</t>
-  </si>
-  <si>
-    <t>37016656000102</t>
-  </si>
-  <si>
-    <t>30348035000187</t>
-  </si>
-  <si>
-    <t>18053359000192</t>
   </si>
   <si>
     <t>28/03/2012</t>
@@ -1979,8 +2006,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1996,7 +2031,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -2004,12 +2039,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2308,85 +2361,85 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:27">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" t="s">
+      <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" t="s">
+      <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2415,32 +2468,32 @@
       <c r="H2" t="s">
         <v>143</v>
       </c>
-      <c r="I2">
-        <v>15280561000169</v>
+      <c r="I2" t="s">
+        <v>216</v>
       </c>
       <c r="J2" t="s">
+        <v>321</v>
+      </c>
+      <c r="K2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L2" t="s">
+        <v>345</v>
+      </c>
+      <c r="M2" t="s">
+        <v>346</v>
+      </c>
+      <c r="N2" t="s">
+        <v>349</v>
+      </c>
+      <c r="O2" t="s">
+        <v>421</v>
+      </c>
+      <c r="P2" t="s">
         <v>216</v>
       </c>
-      <c r="K2" t="s">
-        <v>237</v>
-      </c>
-      <c r="L2" t="s">
-        <v>240</v>
-      </c>
-      <c r="M2" t="s">
-        <v>241</v>
-      </c>
-      <c r="N2" t="s">
-        <v>244</v>
-      </c>
-      <c r="O2" t="s">
-        <v>316</v>
-      </c>
-      <c r="P2" t="s">
-        <v>317</v>
-      </c>
       <c r="Q2" t="s">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="R2">
         <v>2012</v>
@@ -2449,22 +2502,22 @@
         <v>14</v>
       </c>
       <c r="T2" t="s">
-        <v>526</v>
+        <v>535</v>
       </c>
       <c r="U2">
         <v>4</v>
       </c>
       <c r="V2" t="s">
-        <v>528</v>
+        <v>537</v>
       </c>
       <c r="X2" t="s">
-        <v>216</v>
+        <v>321</v>
       </c>
       <c r="Y2" t="s">
-        <v>599</v>
+        <v>608</v>
       </c>
       <c r="Z2" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
@@ -2495,32 +2548,32 @@
       <c r="H3" t="s">
         <v>144</v>
       </c>
-      <c r="I3">
-        <v>3070546000107</v>
+      <c r="I3" t="s">
+        <v>217</v>
       </c>
       <c r="J3" t="s">
-        <v>217</v>
+        <v>322</v>
       </c>
       <c r="K3" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L3" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M3" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="N3" t="s">
-        <v>245</v>
+        <v>350</v>
       </c>
       <c r="O3" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P3" t="s">
-        <v>318</v>
+        <v>422</v>
       </c>
       <c r="Q3" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="R3">
         <v>1999</v>
@@ -2529,25 +2582,25 @@
         <v>27</v>
       </c>
       <c r="T3" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U3">
         <v>2</v>
       </c>
       <c r="V3" t="s">
-        <v>529</v>
+        <v>538</v>
       </c>
       <c r="W3" t="s">
-        <v>537</v>
+        <v>546</v>
       </c>
       <c r="X3" t="s">
-        <v>587</v>
+        <v>596</v>
       </c>
       <c r="Y3" t="s">
-        <v>600</v>
+        <v>609</v>
       </c>
       <c r="Z3" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA3" t="b">
         <v>1</v>
@@ -2578,32 +2631,32 @@
       <c r="H4" t="s">
         <v>145</v>
       </c>
-      <c r="I4">
-        <v>64414622000149</v>
+      <c r="I4" t="s">
+        <v>218</v>
       </c>
       <c r="J4" t="s">
+        <v>323</v>
+      </c>
+      <c r="K4" t="s">
+        <v>342</v>
+      </c>
+      <c r="L4" t="s">
+        <v>345</v>
+      </c>
+      <c r="M4" t="s">
+        <v>347</v>
+      </c>
+      <c r="N4" t="s">
+        <v>351</v>
+      </c>
+      <c r="O4" t="s">
+        <v>421</v>
+      </c>
+      <c r="P4" t="s">
         <v>218</v>
       </c>
-      <c r="K4" t="s">
-        <v>237</v>
-      </c>
-      <c r="L4" t="s">
-        <v>240</v>
-      </c>
-      <c r="M4" t="s">
-        <v>242</v>
-      </c>
-      <c r="N4" t="s">
-        <v>246</v>
-      </c>
-      <c r="O4" t="s">
-        <v>316</v>
-      </c>
-      <c r="P4" t="s">
-        <v>319</v>
-      </c>
       <c r="Q4" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="R4">
         <v>2026</v>
@@ -2612,25 +2665,25 @@
         <v>0</v>
       </c>
       <c r="T4" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U4">
         <v>2</v>
       </c>
       <c r="V4" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="W4" t="s">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="X4" t="s">
-        <v>587</v>
+        <v>596</v>
       </c>
       <c r="Y4" t="s">
-        <v>601</v>
+        <v>610</v>
       </c>
       <c r="Z4" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA4" t="b">
         <v>1</v>
@@ -2661,32 +2714,32 @@
       <c r="H5" t="s">
         <v>146</v>
       </c>
-      <c r="I5">
-        <v>48562907000170</v>
+      <c r="I5" t="s">
+        <v>219</v>
       </c>
       <c r="J5" t="s">
-        <v>218</v>
+        <v>323</v>
       </c>
       <c r="K5" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L5" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M5" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="N5" t="s">
-        <v>247</v>
+        <v>352</v>
       </c>
       <c r="O5" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P5" t="s">
-        <v>320</v>
+        <v>219</v>
       </c>
       <c r="Q5" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="R5">
         <v>2022</v>
@@ -2695,25 +2748,25 @@
         <v>4</v>
       </c>
       <c r="T5" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U5">
         <v>2</v>
       </c>
       <c r="V5" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="W5" t="s">
-        <v>539</v>
+        <v>548</v>
       </c>
       <c r="X5" t="s">
-        <v>587</v>
+        <v>596</v>
       </c>
       <c r="Y5" t="s">
-        <v>602</v>
+        <v>611</v>
       </c>
       <c r="Z5" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA5" t="b">
         <v>1</v>
@@ -2744,32 +2797,32 @@
       <c r="H6" t="s">
         <v>147</v>
       </c>
-      <c r="I6">
-        <v>7274690000116</v>
+      <c r="I6" t="s">
+        <v>220</v>
       </c>
       <c r="J6" t="s">
-        <v>218</v>
+        <v>323</v>
       </c>
       <c r="K6" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L6" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M6" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="N6" t="s">
-        <v>248</v>
+        <v>353</v>
       </c>
       <c r="O6" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P6" t="s">
-        <v>321</v>
+        <v>423</v>
       </c>
       <c r="Q6" t="s">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="R6">
         <v>2005</v>
@@ -2778,25 +2831,25 @@
         <v>21</v>
       </c>
       <c r="T6" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U6">
         <v>2</v>
       </c>
       <c r="V6" t="s">
-        <v>530</v>
+        <v>539</v>
       </c>
       <c r="W6" t="s">
-        <v>540</v>
+        <v>549</v>
       </c>
       <c r="X6" t="s">
-        <v>587</v>
+        <v>596</v>
       </c>
       <c r="Y6" t="s">
-        <v>603</v>
+        <v>612</v>
       </c>
       <c r="Z6" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA6" t="b">
         <v>1</v>
@@ -2827,32 +2880,32 @@
       <c r="H7" t="s">
         <v>148</v>
       </c>
-      <c r="I7">
-        <v>55333145000104</v>
+      <c r="I7" t="s">
+        <v>221</v>
       </c>
       <c r="J7" t="s">
-        <v>218</v>
+        <v>323</v>
       </c>
       <c r="K7" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L7" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M7" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="N7" t="s">
-        <v>249</v>
+        <v>354</v>
       </c>
       <c r="O7" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P7" t="s">
-        <v>322</v>
+        <v>221</v>
       </c>
       <c r="Q7" t="s">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="R7">
         <v>2024</v>
@@ -2861,25 +2914,25 @@
         <v>2</v>
       </c>
       <c r="T7" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U7">
         <v>2</v>
       </c>
       <c r="V7" t="s">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="W7" t="s">
-        <v>541</v>
+        <v>550</v>
       </c>
       <c r="X7" t="s">
-        <v>587</v>
+        <v>596</v>
       </c>
       <c r="Y7" t="s">
-        <v>604</v>
+        <v>613</v>
       </c>
       <c r="Z7" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA7" t="b">
         <v>1</v>
@@ -2910,32 +2963,32 @@
       <c r="H8" t="s">
         <v>149</v>
       </c>
-      <c r="I8">
-        <v>52261829000141</v>
+      <c r="I8" t="s">
+        <v>222</v>
       </c>
       <c r="J8" t="s">
-        <v>218</v>
+        <v>323</v>
       </c>
       <c r="K8" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L8" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M8" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="N8" t="s">
-        <v>250</v>
+        <v>355</v>
       </c>
       <c r="O8" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P8" t="s">
-        <v>323</v>
+        <v>222</v>
       </c>
       <c r="Q8" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="R8">
         <v>2023</v>
@@ -2944,25 +2997,25 @@
         <v>3</v>
       </c>
       <c r="T8" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U8">
         <v>2</v>
       </c>
       <c r="V8" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="W8" t="s">
-        <v>542</v>
+        <v>551</v>
       </c>
       <c r="X8" t="s">
-        <v>587</v>
+        <v>596</v>
       </c>
       <c r="Y8" t="s">
-        <v>605</v>
+        <v>614</v>
       </c>
       <c r="Z8" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA8" t="b">
         <v>1</v>
@@ -2990,32 +3043,32 @@
       <c r="G9" t="s">
         <v>45</v>
       </c>
-      <c r="I9">
-        <v>55029745000175</v>
+      <c r="I9" t="s">
+        <v>223</v>
       </c>
       <c r="J9" t="s">
-        <v>219</v>
+        <v>324</v>
       </c>
       <c r="K9" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L9" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M9" t="s">
-        <v>241</v>
+        <v>346</v>
       </c>
       <c r="N9" t="s">
-        <v>251</v>
+        <v>356</v>
       </c>
       <c r="O9" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P9" t="s">
-        <v>324</v>
+        <v>223</v>
       </c>
       <c r="Q9" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="R9">
         <v>2024</v>
@@ -3024,22 +3077,22 @@
         <v>2</v>
       </c>
       <c r="T9" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U9">
         <v>2</v>
       </c>
       <c r="V9" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="X9" t="s">
-        <v>219</v>
+        <v>324</v>
       </c>
       <c r="Y9" t="s">
-        <v>606</v>
+        <v>615</v>
       </c>
       <c r="Z9" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA9" t="b">
         <v>1</v>
@@ -3070,32 +3123,32 @@
       <c r="H10" t="s">
         <v>150</v>
       </c>
-      <c r="I10">
-        <v>29237543000109</v>
+      <c r="I10" t="s">
+        <v>224</v>
       </c>
       <c r="J10" t="s">
-        <v>218</v>
+        <v>323</v>
       </c>
       <c r="K10" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L10" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M10" t="s">
-        <v>241</v>
+        <v>346</v>
       </c>
       <c r="N10" t="s">
-        <v>252</v>
+        <v>357</v>
       </c>
       <c r="O10" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P10" t="s">
-        <v>325</v>
+        <v>224</v>
       </c>
       <c r="Q10" t="s">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="R10">
         <v>2017</v>
@@ -3104,22 +3157,22 @@
         <v>9</v>
       </c>
       <c r="T10" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U10">
         <v>2</v>
       </c>
       <c r="V10" t="s">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="X10" t="s">
-        <v>588</v>
+        <v>597</v>
       </c>
       <c r="Y10" t="s">
-        <v>607</v>
+        <v>616</v>
       </c>
       <c r="Z10" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA10" t="b">
         <v>1</v>
@@ -3147,32 +3200,32 @@
       <c r="G11" t="s">
         <v>47</v>
       </c>
-      <c r="I11">
-        <v>36601122000180</v>
+      <c r="I11" t="s">
+        <v>225</v>
       </c>
       <c r="J11" t="s">
-        <v>220</v>
+        <v>325</v>
       </c>
       <c r="K11" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L11" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M11" t="s">
-        <v>241</v>
+        <v>346</v>
       </c>
       <c r="N11" t="s">
-        <v>253</v>
+        <v>358</v>
       </c>
       <c r="O11" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P11" t="s">
-        <v>326</v>
+        <v>225</v>
       </c>
       <c r="Q11" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="R11">
         <v>2020</v>
@@ -3181,22 +3234,22 @@
         <v>6</v>
       </c>
       <c r="T11" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U11">
         <v>2</v>
       </c>
       <c r="V11" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="X11" t="s">
-        <v>589</v>
+        <v>598</v>
       </c>
       <c r="Y11" t="s">
-        <v>608</v>
+        <v>617</v>
       </c>
       <c r="Z11" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA11" t="b">
         <v>1</v>
@@ -3227,32 +3280,32 @@
       <c r="H12" t="s">
         <v>151</v>
       </c>
-      <c r="I12">
-        <v>40837487000186</v>
+      <c r="I12" t="s">
+        <v>226</v>
       </c>
       <c r="J12" t="s">
-        <v>218</v>
+        <v>323</v>
       </c>
       <c r="K12" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L12" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M12" t="s">
-        <v>241</v>
+        <v>346</v>
       </c>
       <c r="N12" t="s">
-        <v>254</v>
+        <v>359</v>
       </c>
       <c r="O12" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P12" t="s">
-        <v>327</v>
+        <v>226</v>
       </c>
       <c r="Q12" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="R12">
         <v>2021</v>
@@ -3261,22 +3314,22 @@
         <v>5</v>
       </c>
       <c r="T12" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U12">
         <v>2</v>
       </c>
       <c r="V12" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="X12" t="s">
-        <v>588</v>
+        <v>597</v>
       </c>
       <c r="Y12" t="s">
-        <v>609</v>
+        <v>618</v>
       </c>
       <c r="Z12" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA12" t="b">
         <v>1</v>
@@ -3304,32 +3357,32 @@
       <c r="G13" t="s">
         <v>49</v>
       </c>
-      <c r="I13">
-        <v>64731620000183</v>
+      <c r="I13" t="s">
+        <v>227</v>
       </c>
       <c r="J13" t="s">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="K13" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L13" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M13" t="s">
-        <v>241</v>
+        <v>346</v>
       </c>
       <c r="N13" t="s">
-        <v>255</v>
+        <v>360</v>
       </c>
       <c r="O13" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P13" t="s">
-        <v>328</v>
+        <v>227</v>
       </c>
       <c r="Q13" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="R13">
         <v>2026</v>
@@ -3338,22 +3391,22 @@
         <v>0</v>
       </c>
       <c r="T13" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U13">
         <v>2</v>
       </c>
       <c r="V13" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="X13" t="s">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="Y13" t="s">
-        <v>610</v>
+        <v>619</v>
       </c>
       <c r="Z13" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA13" t="b">
         <v>1</v>
@@ -3381,32 +3434,32 @@
       <c r="G14" t="s">
         <v>50</v>
       </c>
-      <c r="I14">
-        <v>65391507000169</v>
+      <c r="I14" t="s">
+        <v>228</v>
       </c>
       <c r="J14" t="s">
-        <v>222</v>
+        <v>327</v>
       </c>
       <c r="K14" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L14" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M14" t="s">
-        <v>241</v>
+        <v>346</v>
       </c>
       <c r="N14" t="s">
-        <v>256</v>
+        <v>361</v>
       </c>
       <c r="O14" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P14" t="s">
-        <v>329</v>
+        <v>228</v>
       </c>
       <c r="Q14" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="R14">
         <v>2026</v>
@@ -3415,22 +3468,22 @@
         <v>0</v>
       </c>
       <c r="T14" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U14">
         <v>2</v>
       </c>
       <c r="V14" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="X14" t="s">
-        <v>222</v>
+        <v>327</v>
       </c>
       <c r="Y14" t="s">
-        <v>611</v>
+        <v>620</v>
       </c>
       <c r="Z14" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA14" t="b">
         <v>1</v>
@@ -3461,32 +3514,32 @@
       <c r="H15" t="s">
         <v>152</v>
       </c>
-      <c r="I15">
-        <v>66276608000151</v>
+      <c r="I15" t="s">
+        <v>229</v>
       </c>
       <c r="J15" t="s">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="K15" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L15" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M15" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="N15" t="s">
-        <v>257</v>
+        <v>362</v>
       </c>
       <c r="O15" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P15" t="s">
-        <v>330</v>
+        <v>229</v>
       </c>
       <c r="Q15" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="R15">
         <v>2026</v>
@@ -3495,25 +3548,25 @@
         <v>0</v>
       </c>
       <c r="T15" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U15">
         <v>2</v>
       </c>
       <c r="V15" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="W15" t="s">
-        <v>543</v>
+        <v>552</v>
       </c>
       <c r="X15" t="s">
-        <v>224</v>
+        <v>329</v>
       </c>
       <c r="Y15" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="Z15" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA15" t="b">
         <v>1</v>
@@ -3544,32 +3597,32 @@
       <c r="H16" t="s">
         <v>153</v>
       </c>
-      <c r="I16">
-        <v>41112807000101</v>
+      <c r="I16" t="s">
+        <v>230</v>
       </c>
       <c r="J16" t="s">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="K16" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L16" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M16" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="N16" t="s">
-        <v>258</v>
+        <v>363</v>
       </c>
       <c r="O16" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P16" t="s">
-        <v>331</v>
+        <v>230</v>
       </c>
       <c r="Q16" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="R16">
         <v>2021</v>
@@ -3578,25 +3631,25 @@
         <v>5</v>
       </c>
       <c r="T16" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U16">
         <v>2</v>
       </c>
       <c r="V16" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="W16" t="s">
-        <v>544</v>
+        <v>553</v>
       </c>
       <c r="X16" t="s">
-        <v>224</v>
+        <v>329</v>
       </c>
       <c r="Y16" t="s">
-        <v>613</v>
+        <v>622</v>
       </c>
       <c r="Z16" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA16" t="b">
         <v>1</v>
@@ -3624,32 +3677,32 @@
       <c r="G17" t="s">
         <v>53</v>
       </c>
-      <c r="I17">
-        <v>51307679000105</v>
+      <c r="I17" t="s">
+        <v>231</v>
       </c>
       <c r="J17" t="s">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="K17" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L17" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M17" t="s">
-        <v>241</v>
+        <v>346</v>
       </c>
       <c r="N17" t="s">
-        <v>259</v>
+        <v>364</v>
       </c>
       <c r="O17" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P17" t="s">
-        <v>332</v>
+        <v>231</v>
       </c>
       <c r="Q17" t="s">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="R17">
         <v>2023</v>
@@ -3658,22 +3711,22 @@
         <v>3</v>
       </c>
       <c r="T17" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U17">
         <v>2</v>
       </c>
       <c r="V17" t="s">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="X17" t="s">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="Y17" t="s">
-        <v>614</v>
+        <v>623</v>
       </c>
       <c r="Z17" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA17" t="b">
         <v>1</v>
@@ -3704,32 +3757,32 @@
       <c r="H18" t="s">
         <v>154</v>
       </c>
-      <c r="I18">
-        <v>32750806000193</v>
+      <c r="I18" t="s">
+        <v>232</v>
       </c>
       <c r="J18" t="s">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="K18" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L18" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M18" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="N18" t="s">
-        <v>260</v>
+        <v>365</v>
       </c>
       <c r="O18" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P18" t="s">
-        <v>333</v>
+        <v>232</v>
       </c>
       <c r="Q18" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="R18">
         <v>2019</v>
@@ -3738,25 +3791,25 @@
         <v>7</v>
       </c>
       <c r="T18" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U18">
         <v>2</v>
       </c>
       <c r="V18" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="W18" t="s">
-        <v>545</v>
+        <v>554</v>
       </c>
       <c r="X18" t="s">
-        <v>224</v>
+        <v>329</v>
       </c>
       <c r="Y18" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="Z18" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA18" t="b">
         <v>1</v>
@@ -3784,32 +3837,32 @@
       <c r="G19" t="s">
         <v>55</v>
       </c>
-      <c r="I19">
-        <v>54889790000137</v>
+      <c r="I19" t="s">
+        <v>233</v>
       </c>
       <c r="J19" t="s">
-        <v>223</v>
+        <v>328</v>
       </c>
       <c r="K19" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L19" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M19" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="N19" t="s">
-        <v>261</v>
+        <v>366</v>
       </c>
       <c r="O19" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P19" t="s">
-        <v>334</v>
+        <v>233</v>
       </c>
       <c r="Q19" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="R19">
         <v>2024</v>
@@ -3818,25 +3871,25 @@
         <v>2</v>
       </c>
       <c r="T19" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U19">
         <v>2</v>
       </c>
       <c r="V19" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="W19" t="s">
-        <v>546</v>
+        <v>555</v>
       </c>
       <c r="X19" t="s">
-        <v>590</v>
+        <v>599</v>
       </c>
       <c r="Y19" t="s">
-        <v>616</v>
+        <v>625</v>
       </c>
       <c r="Z19" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA19" t="b">
         <v>1</v>
@@ -3867,32 +3920,32 @@
       <c r="H20" t="s">
         <v>155</v>
       </c>
-      <c r="I20">
-        <v>34699213000175</v>
+      <c r="I20" t="s">
+        <v>234</v>
       </c>
       <c r="J20" t="s">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="K20" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L20" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M20" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="N20" t="s">
-        <v>262</v>
+        <v>367</v>
       </c>
       <c r="O20" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P20" t="s">
-        <v>335</v>
+        <v>234</v>
       </c>
       <c r="Q20" t="s">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="R20">
         <v>2019</v>
@@ -3901,25 +3954,25 @@
         <v>7</v>
       </c>
       <c r="T20" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U20">
         <v>2</v>
       </c>
       <c r="V20" t="s">
-        <v>531</v>
+        <v>540</v>
       </c>
       <c r="W20" t="s">
-        <v>547</v>
+        <v>556</v>
       </c>
       <c r="X20" t="s">
-        <v>224</v>
+        <v>329</v>
       </c>
       <c r="Y20" t="s">
-        <v>611</v>
+        <v>620</v>
       </c>
       <c r="Z20" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA20" t="b">
         <v>1</v>
@@ -3950,32 +4003,32 @@
       <c r="H21" t="s">
         <v>156</v>
       </c>
-      <c r="I21">
-        <v>9422273000107</v>
+      <c r="I21" t="s">
+        <v>235</v>
       </c>
       <c r="J21" t="s">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="K21" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L21" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M21" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="N21" t="s">
-        <v>263</v>
+        <v>368</v>
       </c>
       <c r="O21" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P21" t="s">
-        <v>336</v>
+        <v>424</v>
       </c>
       <c r="Q21" t="s">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="R21">
         <v>2008</v>
@@ -3984,25 +4037,25 @@
         <v>18</v>
       </c>
       <c r="T21" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U21">
         <v>2</v>
       </c>
       <c r="V21" t="s">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="W21" t="s">
         <v>57</v>
       </c>
       <c r="X21" t="s">
-        <v>224</v>
+        <v>329</v>
       </c>
       <c r="Y21" t="s">
-        <v>617</v>
+        <v>626</v>
       </c>
       <c r="Z21" t="s">
-        <v>243</v>
+        <v>348</v>
       </c>
       <c r="AA21" t="b">
         <v>1</v>
@@ -4033,32 +4086,32 @@
       <c r="H22" t="s">
         <v>157</v>
       </c>
-      <c r="I22">
-        <v>13159001000125</v>
+      <c r="I22" t="s">
+        <v>236</v>
       </c>
       <c r="J22" t="s">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="K22" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L22" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M22" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="N22" t="s">
-        <v>264</v>
+        <v>369</v>
       </c>
       <c r="O22" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P22" t="s">
-        <v>337</v>
+        <v>236</v>
       </c>
       <c r="Q22" t="s">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="R22">
         <v>2011</v>
@@ -4067,25 +4120,25 @@
         <v>15</v>
       </c>
       <c r="T22" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U22">
         <v>2</v>
       </c>
       <c r="V22" t="s">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="W22" t="s">
-        <v>548</v>
+        <v>557</v>
       </c>
       <c r="X22" t="s">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="Y22" t="s">
-        <v>618</v>
+        <v>627</v>
       </c>
       <c r="Z22" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA22" t="b">
         <v>1</v>
@@ -4116,32 +4169,32 @@
       <c r="H23" t="s">
         <v>158</v>
       </c>
-      <c r="I23">
-        <v>49313373000101</v>
+      <c r="I23" t="s">
+        <v>237</v>
       </c>
       <c r="J23" t="s">
-        <v>224</v>
+        <v>329</v>
       </c>
       <c r="K23" t="s">
-        <v>238</v>
+        <v>343</v>
       </c>
       <c r="L23" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M23" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="N23" t="s">
-        <v>265</v>
+        <v>370</v>
       </c>
       <c r="O23" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P23" t="s">
-        <v>338</v>
+        <v>237</v>
       </c>
       <c r="Q23" t="s">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="R23">
         <v>2023</v>
@@ -4150,25 +4203,25 @@
         <v>3</v>
       </c>
       <c r="T23" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U23">
         <v>2</v>
       </c>
       <c r="V23" t="s">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="W23" t="s">
-        <v>549</v>
+        <v>558</v>
       </c>
       <c r="X23" t="s">
-        <v>224</v>
+        <v>329</v>
       </c>
       <c r="Y23" t="s">
-        <v>619</v>
+        <v>628</v>
       </c>
       <c r="Z23" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA23" t="b">
         <v>1</v>
@@ -4199,32 +4252,32 @@
       <c r="H24" t="s">
         <v>159</v>
       </c>
-      <c r="I24">
-        <v>29530344000194</v>
+      <c r="I24" t="s">
+        <v>238</v>
       </c>
       <c r="J24" t="s">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="K24" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L24" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M24" t="s">
-        <v>241</v>
+        <v>346</v>
       </c>
       <c r="N24" t="s">
-        <v>266</v>
+        <v>371</v>
       </c>
       <c r="O24" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P24" t="s">
-        <v>339</v>
+        <v>238</v>
       </c>
       <c r="Q24" t="s">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="R24">
         <v>2018</v>
@@ -4233,22 +4286,22 @@
         <v>8</v>
       </c>
       <c r="T24" t="s">
-        <v>526</v>
+        <v>535</v>
       </c>
       <c r="U24">
         <v>4</v>
       </c>
       <c r="V24" t="s">
-        <v>532</v>
+        <v>541</v>
       </c>
       <c r="X24" t="s">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="Y24" t="s">
-        <v>620</v>
+        <v>629</v>
       </c>
       <c r="Z24" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA24" t="b">
         <v>0</v>
@@ -4276,32 +4329,32 @@
       <c r="G25" t="s">
         <v>61</v>
       </c>
-      <c r="I25">
-        <v>63970774000165</v>
+      <c r="I25" t="s">
+        <v>239</v>
       </c>
       <c r="J25" t="s">
-        <v>225</v>
+        <v>330</v>
       </c>
       <c r="K25" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L25" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M25" t="s">
-        <v>241</v>
+        <v>346</v>
       </c>
       <c r="N25" t="s">
-        <v>267</v>
+        <v>372</v>
       </c>
       <c r="O25" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P25" t="s">
-        <v>340</v>
+        <v>239</v>
       </c>
       <c r="Q25" t="s">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="R25">
         <v>2025</v>
@@ -4310,22 +4363,22 @@
         <v>1</v>
       </c>
       <c r="T25" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U25">
         <v>2</v>
       </c>
       <c r="V25" t="s">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="X25" t="s">
-        <v>591</v>
+        <v>600</v>
       </c>
       <c r="Y25" t="s">
-        <v>621</v>
+        <v>630</v>
       </c>
       <c r="Z25" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA25" t="b">
         <v>1</v>
@@ -4353,23 +4406,23 @@
       <c r="G26" t="s">
         <v>62</v>
       </c>
-      <c r="I26">
-        <v>57013589000180</v>
+      <c r="I26" t="s">
+        <v>240</v>
       </c>
       <c r="M26" t="s">
-        <v>241</v>
+        <v>346</v>
       </c>
       <c r="N26" t="s">
-        <v>268</v>
+        <v>373</v>
       </c>
       <c r="O26" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P26" t="s">
-        <v>341</v>
+        <v>240</v>
       </c>
       <c r="Q26" t="s">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="R26">
         <v>2024</v>
@@ -4378,22 +4431,22 @@
         <v>2</v>
       </c>
       <c r="T26" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U26">
         <v>2</v>
       </c>
       <c r="V26" t="s">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="X26" t="s">
-        <v>588</v>
+        <v>597</v>
       </c>
       <c r="Y26" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="Z26" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA26" t="b">
         <v>1</v>
@@ -4424,32 +4477,32 @@
       <c r="H27" t="s">
         <v>160</v>
       </c>
-      <c r="I27">
-        <v>11635824000154</v>
+      <c r="I27" t="s">
+        <v>241</v>
       </c>
       <c r="J27" t="s">
-        <v>218</v>
+        <v>323</v>
       </c>
       <c r="K27" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L27" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M27" t="s">
+        <v>346</v>
+      </c>
+      <c r="N27" t="s">
+        <v>374</v>
+      </c>
+      <c r="O27" t="s">
+        <v>421</v>
+      </c>
+      <c r="P27" t="s">
         <v>241</v>
       </c>
-      <c r="N27" t="s">
-        <v>269</v>
-      </c>
-      <c r="O27" t="s">
-        <v>316</v>
-      </c>
-      <c r="P27" t="s">
-        <v>342</v>
-      </c>
       <c r="Q27" t="s">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="R27">
         <v>2010</v>
@@ -4458,22 +4511,22 @@
         <v>16</v>
       </c>
       <c r="T27" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U27">
         <v>2</v>
       </c>
       <c r="V27" t="s">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="X27" t="s">
-        <v>588</v>
+        <v>597</v>
       </c>
       <c r="Y27" t="s">
-        <v>621</v>
+        <v>630</v>
       </c>
       <c r="Z27" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA27" t="b">
         <v>1</v>
@@ -4504,32 +4557,32 @@
       <c r="H28" t="s">
         <v>161</v>
       </c>
-      <c r="I28">
-        <v>64927707000120</v>
+      <c r="I28" t="s">
+        <v>242</v>
       </c>
       <c r="J28" t="s">
-        <v>218</v>
+        <v>323</v>
       </c>
       <c r="K28" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L28" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M28" t="s">
+        <v>347</v>
+      </c>
+      <c r="N28" t="s">
+        <v>375</v>
+      </c>
+      <c r="O28" t="s">
+        <v>421</v>
+      </c>
+      <c r="P28" t="s">
         <v>242</v>
       </c>
-      <c r="N28" t="s">
-        <v>270</v>
-      </c>
-      <c r="O28" t="s">
-        <v>316</v>
-      </c>
-      <c r="P28" t="s">
-        <v>343</v>
-      </c>
       <c r="Q28" t="s">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="R28">
         <v>2026</v>
@@ -4538,25 +4591,25 @@
         <v>0</v>
       </c>
       <c r="T28" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U28">
         <v>2</v>
       </c>
       <c r="V28" t="s">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="W28" t="s">
-        <v>550</v>
+        <v>559</v>
       </c>
       <c r="X28" t="s">
-        <v>587</v>
+        <v>596</v>
       </c>
       <c r="Y28" t="s">
-        <v>600</v>
+        <v>609</v>
       </c>
       <c r="Z28" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA28" t="b">
         <v>1</v>
@@ -4587,32 +4640,32 @@
       <c r="H29" t="s">
         <v>162</v>
       </c>
-      <c r="I29">
-        <v>40050453000147</v>
+      <c r="I29" t="s">
+        <v>243</v>
       </c>
       <c r="J29" t="s">
-        <v>218</v>
+        <v>323</v>
       </c>
       <c r="K29" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L29" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M29" t="s">
-        <v>241</v>
+        <v>346</v>
       </c>
       <c r="N29" t="s">
-        <v>271</v>
+        <v>376</v>
       </c>
       <c r="O29" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P29" t="s">
-        <v>344</v>
+        <v>243</v>
       </c>
       <c r="Q29" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="R29">
         <v>2020</v>
@@ -4621,22 +4674,22 @@
         <v>6</v>
       </c>
       <c r="T29" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U29">
         <v>2</v>
       </c>
       <c r="V29" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="X29" t="s">
-        <v>588</v>
+        <v>597</v>
       </c>
       <c r="Y29" t="s">
-        <v>611</v>
+        <v>620</v>
       </c>
       <c r="Z29" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA29" t="b">
         <v>1</v>
@@ -4664,32 +4717,32 @@
       <c r="G30" t="s">
         <v>66</v>
       </c>
-      <c r="I30">
-        <v>59834120000137</v>
+      <c r="I30" t="s">
+        <v>244</v>
       </c>
       <c r="J30" t="s">
-        <v>218</v>
+        <v>323</v>
       </c>
       <c r="K30" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L30" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M30" t="s">
-        <v>241</v>
+        <v>346</v>
       </c>
       <c r="N30" t="s">
-        <v>272</v>
+        <v>377</v>
       </c>
       <c r="O30" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P30" t="s">
-        <v>345</v>
+        <v>244</v>
       </c>
       <c r="Q30" t="s">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="R30">
         <v>2025</v>
@@ -4698,22 +4751,22 @@
         <v>1</v>
       </c>
       <c r="T30" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U30">
         <v>2</v>
       </c>
       <c r="V30" t="s">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="X30" t="s">
-        <v>588</v>
+        <v>597</v>
       </c>
       <c r="Y30" t="s">
-        <v>602</v>
+        <v>611</v>
       </c>
       <c r="Z30" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA30" t="b">
         <v>1</v>
@@ -4744,32 +4797,32 @@
       <c r="H31" t="s">
         <v>163</v>
       </c>
-      <c r="I31">
-        <v>12962386000100</v>
+      <c r="I31" t="s">
+        <v>245</v>
       </c>
       <c r="J31" t="s">
-        <v>218</v>
+        <v>323</v>
       </c>
       <c r="K31" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L31" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M31" t="s">
-        <v>241</v>
+        <v>346</v>
       </c>
       <c r="N31" t="s">
-        <v>273</v>
+        <v>378</v>
       </c>
       <c r="O31" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P31" t="s">
-        <v>346</v>
+        <v>245</v>
       </c>
       <c r="Q31" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="R31">
         <v>2010</v>
@@ -4778,22 +4831,22 @@
         <v>16</v>
       </c>
       <c r="T31" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U31">
         <v>2</v>
       </c>
       <c r="V31" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="X31" t="s">
-        <v>588</v>
+        <v>597</v>
       </c>
       <c r="Y31" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="Z31" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA31" t="b">
         <v>1</v>
@@ -4824,32 +4877,32 @@
       <c r="H32" t="s">
         <v>164</v>
       </c>
-      <c r="I32">
-        <v>32484626000107</v>
+      <c r="I32" t="s">
+        <v>246</v>
       </c>
       <c r="J32" t="s">
-        <v>218</v>
+        <v>323</v>
       </c>
       <c r="K32" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L32" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M32" t="s">
-        <v>241</v>
+        <v>346</v>
       </c>
       <c r="N32" t="s">
-        <v>274</v>
+        <v>379</v>
       </c>
       <c r="O32" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P32" t="s">
-        <v>347</v>
+        <v>246</v>
       </c>
       <c r="Q32" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="R32">
         <v>2019</v>
@@ -4858,22 +4911,22 @@
         <v>7</v>
       </c>
       <c r="T32" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U32">
         <v>2</v>
       </c>
       <c r="V32" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="X32" t="s">
-        <v>588</v>
+        <v>597</v>
       </c>
       <c r="Y32" t="s">
-        <v>620</v>
+        <v>629</v>
       </c>
       <c r="Z32" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA32" t="b">
         <v>1</v>
@@ -4901,32 +4954,32 @@
       <c r="G33" t="s">
         <v>69</v>
       </c>
-      <c r="I33">
-        <v>63364739000100</v>
+      <c r="I33" t="s">
+        <v>247</v>
       </c>
       <c r="J33" t="s">
-        <v>226</v>
+        <v>331</v>
       </c>
       <c r="K33" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L33" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M33" t="s">
-        <v>241</v>
+        <v>346</v>
       </c>
       <c r="N33" t="s">
-        <v>275</v>
+        <v>380</v>
       </c>
       <c r="O33" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P33" t="s">
-        <v>348</v>
+        <v>247</v>
       </c>
       <c r="Q33" t="s">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="R33">
         <v>2025</v>
@@ -4935,22 +4988,22 @@
         <v>1</v>
       </c>
       <c r="T33" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U33">
         <v>2</v>
       </c>
       <c r="V33" t="s">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="X33" t="s">
-        <v>226</v>
+        <v>331</v>
       </c>
       <c r="Y33" t="s">
-        <v>622</v>
+        <v>631</v>
       </c>
       <c r="Z33" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA33" t="b">
         <v>1</v>
@@ -4978,32 +5031,32 @@
       <c r="G34" t="s">
         <v>70</v>
       </c>
-      <c r="I34">
-        <v>60394938000165</v>
+      <c r="I34" t="s">
+        <v>248</v>
       </c>
       <c r="J34" t="s">
-        <v>218</v>
+        <v>323</v>
       </c>
       <c r="K34" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L34" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M34" t="s">
-        <v>241</v>
+        <v>346</v>
       </c>
       <c r="N34" t="s">
-        <v>276</v>
+        <v>381</v>
       </c>
       <c r="O34" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P34" t="s">
-        <v>349</v>
+        <v>248</v>
       </c>
       <c r="Q34" t="s">
-        <v>454</v>
+        <v>463</v>
       </c>
       <c r="R34">
         <v>2025</v>
@@ -5012,22 +5065,22 @@
         <v>1</v>
       </c>
       <c r="T34" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U34">
         <v>2</v>
       </c>
       <c r="V34" t="s">
-        <v>454</v>
+        <v>463</v>
       </c>
       <c r="X34" t="s">
-        <v>588</v>
+        <v>597</v>
       </c>
       <c r="Y34" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="Z34" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA34" t="b">
         <v>1</v>
@@ -5055,32 +5108,32 @@
       <c r="G35" t="s">
         <v>71</v>
       </c>
-      <c r="I35">
-        <v>54448012000102</v>
+      <c r="I35" t="s">
+        <v>249</v>
       </c>
       <c r="J35" t="s">
-        <v>218</v>
+        <v>323</v>
       </c>
       <c r="K35" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L35" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M35" t="s">
-        <v>241</v>
+        <v>346</v>
       </c>
       <c r="N35" t="s">
-        <v>277</v>
+        <v>382</v>
       </c>
       <c r="O35" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P35" t="s">
-        <v>350</v>
+        <v>249</v>
       </c>
       <c r="Q35" t="s">
-        <v>455</v>
+        <v>464</v>
       </c>
       <c r="R35">
         <v>2024</v>
@@ -5089,22 +5142,22 @@
         <v>2</v>
       </c>
       <c r="T35" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U35">
         <v>2</v>
       </c>
       <c r="V35" t="s">
-        <v>455</v>
+        <v>464</v>
       </c>
       <c r="X35" t="s">
-        <v>588</v>
+        <v>597</v>
       </c>
       <c r="Y35" t="s">
-        <v>623</v>
+        <v>632</v>
       </c>
       <c r="Z35" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA35" t="b">
         <v>1</v>
@@ -5132,32 +5185,32 @@
       <c r="G36" t="s">
         <v>72</v>
       </c>
-      <c r="I36">
-        <v>59209988000146</v>
+      <c r="I36" t="s">
+        <v>250</v>
       </c>
       <c r="J36" t="s">
-        <v>218</v>
+        <v>323</v>
       </c>
       <c r="K36" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L36" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M36" t="s">
-        <v>241</v>
+        <v>346</v>
       </c>
       <c r="N36" t="s">
-        <v>278</v>
+        <v>383</v>
       </c>
       <c r="O36" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P36" t="s">
-        <v>351</v>
+        <v>250</v>
       </c>
       <c r="Q36" t="s">
-        <v>456</v>
+        <v>465</v>
       </c>
       <c r="R36">
         <v>2025</v>
@@ -5166,22 +5219,22 @@
         <v>1</v>
       </c>
       <c r="T36" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U36">
         <v>2</v>
       </c>
       <c r="V36" t="s">
-        <v>456</v>
+        <v>465</v>
       </c>
       <c r="X36" t="s">
-        <v>588</v>
+        <v>597</v>
       </c>
       <c r="Y36" t="s">
-        <v>611</v>
+        <v>620</v>
       </c>
       <c r="Z36" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA36" t="b">
         <v>1</v>
@@ -5212,32 +5265,32 @@
       <c r="H37" t="s">
         <v>165</v>
       </c>
-      <c r="I37">
-        <v>39288435000119</v>
+      <c r="I37" t="s">
+        <v>251</v>
       </c>
       <c r="J37" t="s">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="K37" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L37" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M37" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="N37" t="s">
-        <v>279</v>
+        <v>384</v>
       </c>
       <c r="O37" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P37" t="s">
-        <v>352</v>
+        <v>251</v>
       </c>
       <c r="Q37" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="R37">
         <v>2020</v>
@@ -5246,25 +5299,25 @@
         <v>6</v>
       </c>
       <c r="T37" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U37">
         <v>2</v>
       </c>
       <c r="V37" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="W37" t="s">
-        <v>551</v>
+        <v>560</v>
       </c>
       <c r="X37" t="s">
-        <v>224</v>
+        <v>329</v>
       </c>
       <c r="Y37" t="s">
-        <v>624</v>
+        <v>633</v>
       </c>
       <c r="Z37" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA37" t="b">
         <v>1</v>
@@ -5295,32 +5348,32 @@
       <c r="H38" t="s">
         <v>166</v>
       </c>
-      <c r="I38">
-        <v>17397084000141</v>
+      <c r="I38" t="s">
+        <v>252</v>
       </c>
       <c r="J38" t="s">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="K38" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L38" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M38" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="N38" t="s">
-        <v>280</v>
+        <v>385</v>
       </c>
       <c r="O38" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P38" t="s">
-        <v>353</v>
+        <v>252</v>
       </c>
       <c r="Q38" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
       <c r="R38">
         <v>1982</v>
@@ -5329,25 +5382,25 @@
         <v>44</v>
       </c>
       <c r="T38" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U38">
         <v>2</v>
       </c>
       <c r="V38" t="s">
-        <v>533</v>
+        <v>542</v>
       </c>
       <c r="W38" t="s">
-        <v>552</v>
+        <v>561</v>
       </c>
       <c r="X38" t="s">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="Y38" t="s">
-        <v>625</v>
+        <v>634</v>
       </c>
       <c r="Z38" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA38" t="b">
         <v>1</v>
@@ -5378,32 +5431,32 @@
       <c r="H39" t="s">
         <v>167</v>
       </c>
-      <c r="I39">
-        <v>37018349000160</v>
+      <c r="I39" t="s">
+        <v>253</v>
       </c>
       <c r="J39" t="s">
-        <v>227</v>
+        <v>332</v>
       </c>
       <c r="K39" t="s">
-        <v>239</v>
+        <v>344</v>
       </c>
       <c r="L39" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M39" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="N39" t="s">
-        <v>281</v>
+        <v>386</v>
       </c>
       <c r="O39" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P39" t="s">
-        <v>354</v>
+        <v>253</v>
       </c>
       <c r="Q39" t="s">
-        <v>459</v>
+        <v>468</v>
       </c>
       <c r="R39">
         <v>2020</v>
@@ -5412,22 +5465,22 @@
         <v>6</v>
       </c>
       <c r="T39" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U39">
         <v>2</v>
       </c>
       <c r="V39" t="s">
-        <v>459</v>
+        <v>468</v>
       </c>
       <c r="X39" t="s">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="Y39" t="s">
-        <v>626</v>
+        <v>635</v>
       </c>
       <c r="Z39" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA39" t="b">
         <v>1</v>
@@ -5455,32 +5508,32 @@
       <c r="G40" t="s">
         <v>76</v>
       </c>
-      <c r="I40">
-        <v>17784817000109</v>
+      <c r="I40" t="s">
+        <v>254</v>
       </c>
       <c r="J40" t="s">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="K40" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L40" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M40" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="N40" t="s">
-        <v>282</v>
+        <v>387</v>
       </c>
       <c r="O40" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P40" t="s">
-        <v>355</v>
+        <v>254</v>
       </c>
       <c r="Q40" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="R40">
         <v>2013</v>
@@ -5489,25 +5542,25 @@
         <v>13</v>
       </c>
       <c r="T40" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U40">
         <v>2</v>
       </c>
       <c r="V40" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="W40" t="s">
-        <v>553</v>
+        <v>562</v>
       </c>
       <c r="X40" t="s">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="Y40" t="s">
-        <v>626</v>
+        <v>635</v>
       </c>
       <c r="Z40" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA40" t="b">
         <v>1</v>
@@ -5538,32 +5591,32 @@
       <c r="H41" t="s">
         <v>168</v>
       </c>
-      <c r="I41">
-        <v>50277820000101</v>
+      <c r="I41" t="s">
+        <v>255</v>
       </c>
       <c r="J41" t="s">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="K41" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L41" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M41" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="N41" t="s">
-        <v>283</v>
+        <v>388</v>
       </c>
       <c r="O41" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P41" t="s">
-        <v>356</v>
+        <v>255</v>
       </c>
       <c r="Q41" t="s">
-        <v>461</v>
+        <v>470</v>
       </c>
       <c r="R41">
         <v>2023</v>
@@ -5572,25 +5625,25 @@
         <v>3</v>
       </c>
       <c r="T41" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U41">
         <v>2</v>
       </c>
       <c r="V41" t="s">
-        <v>461</v>
+        <v>470</v>
       </c>
       <c r="W41" t="s">
-        <v>554</v>
+        <v>563</v>
       </c>
       <c r="X41" t="s">
-        <v>224</v>
+        <v>329</v>
       </c>
       <c r="Y41" t="s">
-        <v>627</v>
+        <v>636</v>
       </c>
       <c r="Z41" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA41" t="b">
         <v>1</v>
@@ -5621,32 +5674,32 @@
       <c r="H42" t="s">
         <v>169</v>
       </c>
-      <c r="I42">
-        <v>24296850000147</v>
+      <c r="I42" t="s">
+        <v>256</v>
       </c>
       <c r="J42" t="s">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="K42" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L42" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M42" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="N42" t="s">
-        <v>284</v>
+        <v>389</v>
       </c>
       <c r="O42" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P42" t="s">
-        <v>357</v>
+        <v>256</v>
       </c>
       <c r="Q42" t="s">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="R42">
         <v>2016</v>
@@ -5655,25 +5708,25 @@
         <v>10</v>
       </c>
       <c r="T42" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U42">
         <v>2</v>
       </c>
       <c r="V42" t="s">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="W42" t="s">
-        <v>555</v>
+        <v>564</v>
       </c>
       <c r="X42" t="s">
-        <v>224</v>
+        <v>329</v>
       </c>
       <c r="Y42" t="s">
-        <v>628</v>
+        <v>637</v>
       </c>
       <c r="Z42" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA42" t="b">
         <v>1</v>
@@ -5704,32 +5757,32 @@
       <c r="H43" t="s">
         <v>170</v>
       </c>
-      <c r="I43">
-        <v>52311623000189</v>
+      <c r="I43" t="s">
+        <v>257</v>
       </c>
       <c r="J43" t="s">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="K43" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L43" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M43" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="N43" t="s">
-        <v>285</v>
+        <v>390</v>
       </c>
       <c r="O43" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P43" t="s">
-        <v>358</v>
+        <v>257</v>
       </c>
       <c r="Q43" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="R43">
         <v>2023</v>
@@ -5738,25 +5791,25 @@
         <v>3</v>
       </c>
       <c r="T43" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U43">
         <v>2</v>
       </c>
       <c r="V43" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="W43" t="s">
-        <v>556</v>
+        <v>565</v>
       </c>
       <c r="X43" t="s">
-        <v>224</v>
+        <v>329</v>
       </c>
       <c r="Y43" t="s">
-        <v>629</v>
+        <v>638</v>
       </c>
       <c r="Z43" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA43" t="b">
         <v>1</v>
@@ -5787,32 +5840,32 @@
       <c r="H44" t="s">
         <v>171</v>
       </c>
-      <c r="I44">
-        <v>19970932000195</v>
+      <c r="I44" t="s">
+        <v>258</v>
       </c>
       <c r="J44" t="s">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="K44" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L44" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M44" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="N44" t="s">
-        <v>286</v>
+        <v>391</v>
       </c>
       <c r="O44" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P44" t="s">
-        <v>359</v>
+        <v>258</v>
       </c>
       <c r="Q44" t="s">
-        <v>464</v>
+        <v>473</v>
       </c>
       <c r="R44">
         <v>2014</v>
@@ -5821,25 +5874,25 @@
         <v>12</v>
       </c>
       <c r="T44" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U44">
         <v>2</v>
       </c>
       <c r="V44" t="s">
-        <v>464</v>
+        <v>473</v>
       </c>
       <c r="W44" t="s">
-        <v>557</v>
+        <v>566</v>
       </c>
       <c r="X44" t="s">
-        <v>224</v>
+        <v>329</v>
       </c>
       <c r="Y44" t="s">
-        <v>617</v>
+        <v>626</v>
       </c>
       <c r="Z44" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA44" t="b">
         <v>1</v>
@@ -5870,32 +5923,32 @@
       <c r="H45" t="s">
         <v>172</v>
       </c>
-      <c r="I45">
-        <v>17473809000133</v>
+      <c r="I45" t="s">
+        <v>259</v>
       </c>
       <c r="J45" t="s">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="K45" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L45" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M45" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="N45" t="s">
-        <v>287</v>
+        <v>392</v>
       </c>
       <c r="O45" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P45" t="s">
-        <v>360</v>
+        <v>259</v>
       </c>
       <c r="Q45" t="s">
-        <v>465</v>
+        <v>474</v>
       </c>
       <c r="R45">
         <v>2013</v>
@@ -5904,25 +5957,25 @@
         <v>13</v>
       </c>
       <c r="T45" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U45">
         <v>2</v>
       </c>
       <c r="V45" t="s">
-        <v>465</v>
+        <v>474</v>
       </c>
       <c r="W45" t="s">
-        <v>558</v>
+        <v>567</v>
       </c>
       <c r="X45" t="s">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="Y45" t="s">
-        <v>601</v>
+        <v>610</v>
       </c>
       <c r="Z45" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA45" t="b">
         <v>1</v>
@@ -5953,32 +6006,32 @@
       <c r="H46" t="s">
         <v>173</v>
       </c>
-      <c r="I46">
-        <v>64620869000111</v>
+      <c r="I46" t="s">
+        <v>260</v>
       </c>
       <c r="J46" t="s">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="K46" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L46" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M46" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="N46" t="s">
-        <v>288</v>
+        <v>393</v>
       </c>
       <c r="O46" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P46" t="s">
-        <v>361</v>
+        <v>260</v>
       </c>
       <c r="Q46" t="s">
-        <v>466</v>
+        <v>475</v>
       </c>
       <c r="R46">
         <v>2026</v>
@@ -5987,25 +6040,25 @@
         <v>0</v>
       </c>
       <c r="T46" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U46">
         <v>2</v>
       </c>
       <c r="V46" t="s">
-        <v>466</v>
+        <v>475</v>
       </c>
       <c r="W46" t="s">
-        <v>559</v>
+        <v>568</v>
       </c>
       <c r="X46" t="s">
-        <v>224</v>
+        <v>329</v>
       </c>
       <c r="Y46" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="Z46" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA46" t="b">
         <v>1</v>
@@ -6033,32 +6086,32 @@
       <c r="G47" t="s">
         <v>83</v>
       </c>
-      <c r="I47">
-        <v>19317140000116</v>
+      <c r="I47" t="s">
+        <v>261</v>
       </c>
       <c r="J47" t="s">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="K47" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L47" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M47" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="N47" t="s">
-        <v>289</v>
+        <v>394</v>
       </c>
       <c r="O47" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P47" t="s">
-        <v>362</v>
+        <v>261</v>
       </c>
       <c r="Q47" t="s">
-        <v>467</v>
+        <v>476</v>
       </c>
       <c r="R47">
         <v>2013</v>
@@ -6067,25 +6120,25 @@
         <v>13</v>
       </c>
       <c r="T47" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U47">
         <v>2</v>
       </c>
       <c r="V47" t="s">
-        <v>467</v>
+        <v>476</v>
       </c>
       <c r="W47" t="s">
-        <v>559</v>
+        <v>568</v>
       </c>
       <c r="X47" t="s">
-        <v>224</v>
+        <v>329</v>
       </c>
       <c r="Y47" t="s">
-        <v>631</v>
+        <v>640</v>
       </c>
       <c r="Z47" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA47" t="b">
         <v>1</v>
@@ -6116,32 +6169,32 @@
       <c r="H48" t="s">
         <v>174</v>
       </c>
-      <c r="I48">
-        <v>47144853000160</v>
+      <c r="I48" t="s">
+        <v>262</v>
       </c>
       <c r="J48" t="s">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="K48" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L48" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M48" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="N48" t="s">
-        <v>290</v>
+        <v>395</v>
       </c>
       <c r="O48" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P48" t="s">
-        <v>363</v>
+        <v>262</v>
       </c>
       <c r="Q48" t="s">
-        <v>468</v>
+        <v>477</v>
       </c>
       <c r="R48">
         <v>2022</v>
@@ -6150,25 +6203,25 @@
         <v>4</v>
       </c>
       <c r="T48" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U48">
         <v>2</v>
       </c>
       <c r="V48" t="s">
-        <v>468</v>
+        <v>477</v>
       </c>
       <c r="W48" t="s">
-        <v>560</v>
+        <v>569</v>
       </c>
       <c r="X48" t="s">
-        <v>224</v>
+        <v>329</v>
       </c>
       <c r="Y48" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="Z48" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA48" t="b">
         <v>1</v>
@@ -6199,32 +6252,32 @@
       <c r="H49" t="s">
         <v>175</v>
       </c>
-      <c r="I49">
-        <v>18530119000131</v>
+      <c r="I49" t="s">
+        <v>263</v>
       </c>
       <c r="J49" t="s">
-        <v>218</v>
+        <v>323</v>
       </c>
       <c r="K49" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L49" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M49" t="s">
-        <v>241</v>
+        <v>346</v>
       </c>
       <c r="N49" t="s">
-        <v>291</v>
+        <v>396</v>
       </c>
       <c r="O49" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P49" t="s">
-        <v>364</v>
+        <v>263</v>
       </c>
       <c r="Q49" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="R49">
         <v>2013</v>
@@ -6233,22 +6286,22 @@
         <v>13</v>
       </c>
       <c r="T49" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U49">
         <v>2</v>
       </c>
       <c r="V49" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="X49" t="s">
-        <v>588</v>
+        <v>597</v>
       </c>
       <c r="Y49" t="s">
-        <v>621</v>
+        <v>630</v>
       </c>
       <c r="Z49" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA49" t="b">
         <v>1</v>
@@ -6279,32 +6332,32 @@
       <c r="H50" t="s">
         <v>176</v>
       </c>
-      <c r="I50">
-        <v>34360182000123</v>
+      <c r="I50" t="s">
+        <v>264</v>
       </c>
       <c r="J50" t="s">
-        <v>218</v>
+        <v>323</v>
       </c>
       <c r="K50" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L50" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M50" t="s">
-        <v>241</v>
+        <v>346</v>
       </c>
       <c r="N50" t="s">
-        <v>292</v>
+        <v>397</v>
       </c>
       <c r="O50" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P50" t="s">
-        <v>365</v>
+        <v>264</v>
       </c>
       <c r="Q50" t="s">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="R50">
         <v>2019</v>
@@ -6313,22 +6366,22 @@
         <v>7</v>
       </c>
       <c r="T50" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U50">
         <v>2</v>
       </c>
       <c r="V50" t="s">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="X50" t="s">
-        <v>588</v>
+        <v>597</v>
       </c>
       <c r="Y50" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="Z50" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA50" t="b">
         <v>1</v>
@@ -6356,32 +6409,32 @@
       <c r="G51" t="s">
         <v>87</v>
       </c>
-      <c r="I51">
-        <v>59137961000195</v>
+      <c r="I51" t="s">
+        <v>265</v>
       </c>
       <c r="J51" t="s">
-        <v>218</v>
+        <v>323</v>
       </c>
       <c r="K51" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L51" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M51" t="s">
-        <v>241</v>
+        <v>346</v>
       </c>
       <c r="N51" t="s">
-        <v>293</v>
+        <v>398</v>
       </c>
       <c r="O51" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P51" t="s">
-        <v>366</v>
+        <v>265</v>
       </c>
       <c r="Q51" t="s">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="R51">
         <v>2025</v>
@@ -6390,22 +6443,22 @@
         <v>1</v>
       </c>
       <c r="T51" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U51">
         <v>2</v>
       </c>
       <c r="V51" t="s">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="X51" t="s">
-        <v>588</v>
+        <v>597</v>
       </c>
       <c r="Y51" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="Z51" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA51" t="b">
         <v>1</v>
@@ -6436,32 +6489,32 @@
       <c r="H52" t="s">
         <v>177</v>
       </c>
-      <c r="I52">
-        <v>14784541000162</v>
+      <c r="I52" t="s">
+        <v>266</v>
       </c>
       <c r="J52" t="s">
-        <v>218</v>
+        <v>323</v>
       </c>
       <c r="K52" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L52" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M52" t="s">
-        <v>241</v>
+        <v>346</v>
       </c>
       <c r="N52" t="s">
-        <v>294</v>
+        <v>399</v>
       </c>
       <c r="O52" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P52" t="s">
-        <v>367</v>
+        <v>266</v>
       </c>
       <c r="Q52" t="s">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="R52">
         <v>2011</v>
@@ -6470,22 +6523,22 @@
         <v>15</v>
       </c>
       <c r="T52" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U52">
         <v>2</v>
       </c>
       <c r="V52" t="s">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="X52" t="s">
-        <v>588</v>
+        <v>597</v>
       </c>
       <c r="Y52" t="s">
-        <v>632</v>
+        <v>641</v>
       </c>
       <c r="Z52" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA52" t="b">
         <v>1</v>
@@ -6516,32 +6569,32 @@
       <c r="H53" t="s">
         <v>178</v>
       </c>
-      <c r="I53">
-        <v>44047970000118</v>
+      <c r="I53" t="s">
+        <v>267</v>
       </c>
       <c r="J53" t="s">
-        <v>228</v>
+        <v>333</v>
       </c>
       <c r="K53" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L53" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M53" t="s">
-        <v>241</v>
+        <v>346</v>
       </c>
       <c r="N53" t="s">
-        <v>295</v>
+        <v>400</v>
       </c>
       <c r="O53" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P53" t="s">
-        <v>368</v>
+        <v>267</v>
       </c>
       <c r="Q53" t="s">
-        <v>473</v>
+        <v>482</v>
       </c>
       <c r="R53">
         <v>2021</v>
@@ -6550,22 +6603,22 @@
         <v>5</v>
       </c>
       <c r="T53" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U53">
         <v>2</v>
       </c>
       <c r="V53" t="s">
-        <v>473</v>
+        <v>482</v>
       </c>
       <c r="X53" t="s">
-        <v>228</v>
+        <v>333</v>
       </c>
       <c r="Y53" t="s">
-        <v>633</v>
+        <v>642</v>
       </c>
       <c r="Z53" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA53" t="b">
         <v>1</v>
@@ -6593,32 +6646,32 @@
       <c r="G54" t="s">
         <v>90</v>
       </c>
-      <c r="I54">
-        <v>60962378000106</v>
+      <c r="I54" t="s">
+        <v>268</v>
       </c>
       <c r="J54" t="s">
-        <v>218</v>
+        <v>323</v>
       </c>
       <c r="K54" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L54" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M54" t="s">
-        <v>241</v>
+        <v>346</v>
       </c>
       <c r="N54" t="s">
-        <v>296</v>
+        <v>401</v>
       </c>
       <c r="O54" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P54" t="s">
-        <v>369</v>
+        <v>268</v>
       </c>
       <c r="Q54" t="s">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="R54">
         <v>2025</v>
@@ -6627,22 +6680,22 @@
         <v>1</v>
       </c>
       <c r="T54" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U54">
         <v>2</v>
       </c>
       <c r="V54" t="s">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="X54" t="s">
-        <v>588</v>
+        <v>597</v>
       </c>
       <c r="Y54" t="s">
-        <v>634</v>
+        <v>643</v>
       </c>
       <c r="Z54" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA54" t="b">
         <v>1</v>
@@ -6673,32 +6726,32 @@
       <c r="H55" t="s">
         <v>179</v>
       </c>
-      <c r="I55">
-        <v>18746186000198</v>
+      <c r="I55" t="s">
+        <v>269</v>
       </c>
       <c r="J55" t="s">
-        <v>218</v>
+        <v>323</v>
       </c>
       <c r="K55" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L55" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M55" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="N55" t="s">
-        <v>297</v>
+        <v>402</v>
       </c>
       <c r="O55" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P55" t="s">
-        <v>370</v>
+        <v>269</v>
       </c>
       <c r="Q55" t="s">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="R55">
         <v>2013</v>
@@ -6707,22 +6760,22 @@
         <v>13</v>
       </c>
       <c r="T55" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U55">
         <v>2</v>
       </c>
       <c r="V55" t="s">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="X55" t="s">
-        <v>588</v>
+        <v>597</v>
       </c>
       <c r="Y55" t="s">
-        <v>611</v>
+        <v>620</v>
       </c>
       <c r="Z55" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA55" t="b">
         <v>1</v>
@@ -6753,32 +6806,32 @@
       <c r="H56" t="s">
         <v>180</v>
       </c>
-      <c r="I56">
-        <v>29696014000173</v>
+      <c r="I56" t="s">
+        <v>270</v>
       </c>
       <c r="J56" t="s">
-        <v>218</v>
+        <v>323</v>
       </c>
       <c r="K56" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L56" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M56" t="s">
-        <v>241</v>
+        <v>346</v>
       </c>
       <c r="N56" t="s">
-        <v>298</v>
+        <v>403</v>
       </c>
       <c r="O56" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P56" t="s">
-        <v>371</v>
+        <v>270</v>
       </c>
       <c r="Q56" t="s">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c r="R56">
         <v>2018</v>
@@ -6787,22 +6840,22 @@
         <v>8</v>
       </c>
       <c r="T56" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U56">
         <v>2</v>
       </c>
       <c r="V56" t="s">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c r="X56" t="s">
-        <v>588</v>
+        <v>597</v>
       </c>
       <c r="Y56" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="Z56" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA56" t="b">
         <v>1</v>
@@ -6833,32 +6886,32 @@
       <c r="H57" t="s">
         <v>181</v>
       </c>
-      <c r="I57">
-        <v>34822047000152</v>
+      <c r="I57" t="s">
+        <v>271</v>
       </c>
       <c r="J57" t="s">
-        <v>218</v>
+        <v>323</v>
       </c>
       <c r="K57" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L57" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M57" t="s">
-        <v>241</v>
+        <v>346</v>
       </c>
       <c r="N57" t="s">
-        <v>299</v>
+        <v>404</v>
       </c>
       <c r="O57" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P57" t="s">
-        <v>372</v>
+        <v>271</v>
       </c>
       <c r="Q57" t="s">
-        <v>477</v>
+        <v>486</v>
       </c>
       <c r="R57">
         <v>2019</v>
@@ -6867,22 +6920,22 @@
         <v>7</v>
       </c>
       <c r="T57" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U57">
         <v>2</v>
       </c>
       <c r="V57" t="s">
-        <v>534</v>
+        <v>543</v>
       </c>
       <c r="X57" t="s">
-        <v>588</v>
+        <v>597</v>
       </c>
       <c r="Y57" t="s">
-        <v>611</v>
+        <v>620</v>
       </c>
       <c r="Z57" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA57" t="b">
         <v>1</v>
@@ -6913,32 +6966,32 @@
       <c r="H58" t="s">
         <v>182</v>
       </c>
-      <c r="I58">
-        <v>52052110000109</v>
+      <c r="I58" t="s">
+        <v>272</v>
       </c>
       <c r="J58" t="s">
-        <v>218</v>
+        <v>323</v>
       </c>
       <c r="K58" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L58" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M58" t="s">
-        <v>241</v>
+        <v>346</v>
       </c>
       <c r="N58" t="s">
-        <v>300</v>
+        <v>405</v>
       </c>
       <c r="O58" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P58" t="s">
-        <v>373</v>
+        <v>272</v>
       </c>
       <c r="Q58" t="s">
-        <v>478</v>
+        <v>487</v>
       </c>
       <c r="R58">
         <v>2023</v>
@@ -6947,22 +7000,22 @@
         <v>3</v>
       </c>
       <c r="T58" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U58">
         <v>2</v>
       </c>
       <c r="V58" t="s">
-        <v>478</v>
+        <v>487</v>
       </c>
       <c r="X58" t="s">
-        <v>588</v>
+        <v>597</v>
       </c>
       <c r="Y58" t="s">
-        <v>635</v>
+        <v>644</v>
       </c>
       <c r="Z58" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA58" t="b">
         <v>1</v>
@@ -6993,32 +7046,32 @@
       <c r="H59" t="s">
         <v>183</v>
       </c>
-      <c r="I59">
-        <v>51227599000131</v>
+      <c r="I59" t="s">
+        <v>273</v>
       </c>
       <c r="J59" t="s">
-        <v>229</v>
+        <v>334</v>
       </c>
       <c r="K59" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L59" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M59" t="s">
-        <v>241</v>
+        <v>346</v>
       </c>
       <c r="N59" t="s">
-        <v>301</v>
+        <v>406</v>
       </c>
       <c r="O59" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P59" t="s">
-        <v>374</v>
+        <v>273</v>
       </c>
       <c r="Q59" t="s">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="R59">
         <v>2023</v>
@@ -7027,22 +7080,22 @@
         <v>3</v>
       </c>
       <c r="T59" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U59">
         <v>2</v>
       </c>
       <c r="V59" t="s">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="X59" t="s">
-        <v>592</v>
+        <v>601</v>
       </c>
       <c r="Y59" t="s">
-        <v>636</v>
+        <v>645</v>
       </c>
       <c r="Z59" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA59" t="b">
         <v>1</v>
@@ -7073,32 +7126,32 @@
       <c r="H60" t="s">
         <v>184</v>
       </c>
-      <c r="I60">
-        <v>33853038000166</v>
+      <c r="I60" t="s">
+        <v>274</v>
       </c>
       <c r="J60" t="s">
-        <v>218</v>
+        <v>323</v>
       </c>
       <c r="K60" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L60" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M60" t="s">
-        <v>241</v>
+        <v>346</v>
       </c>
       <c r="N60" t="s">
-        <v>302</v>
+        <v>407</v>
       </c>
       <c r="O60" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P60" t="s">
-        <v>375</v>
+        <v>274</v>
       </c>
       <c r="Q60" t="s">
-        <v>480</v>
+        <v>489</v>
       </c>
       <c r="R60">
         <v>2019</v>
@@ -7107,22 +7160,22 @@
         <v>7</v>
       </c>
       <c r="T60" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U60">
         <v>2</v>
       </c>
       <c r="V60" t="s">
-        <v>480</v>
+        <v>489</v>
       </c>
       <c r="X60" t="s">
-        <v>588</v>
+        <v>597</v>
       </c>
       <c r="Y60" t="s">
-        <v>621</v>
+        <v>630</v>
       </c>
       <c r="Z60" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA60" t="b">
         <v>1</v>
@@ -7153,32 +7206,32 @@
       <c r="H61" t="s">
         <v>185</v>
       </c>
-      <c r="I61">
-        <v>23248210000107</v>
+      <c r="I61" t="s">
+        <v>275</v>
       </c>
       <c r="J61" t="s">
-        <v>218</v>
+        <v>323</v>
       </c>
       <c r="K61" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L61" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M61" t="s">
-        <v>241</v>
+        <v>346</v>
       </c>
       <c r="N61" t="s">
-        <v>303</v>
+        <v>408</v>
       </c>
       <c r="O61" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P61" t="s">
-        <v>376</v>
+        <v>275</v>
       </c>
       <c r="Q61" t="s">
-        <v>481</v>
+        <v>490</v>
       </c>
       <c r="R61">
         <v>2015</v>
@@ -7187,22 +7240,22 @@
         <v>11</v>
       </c>
       <c r="T61" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U61">
         <v>2</v>
       </c>
       <c r="V61" t="s">
-        <v>481</v>
+        <v>490</v>
       </c>
       <c r="X61" t="s">
-        <v>593</v>
+        <v>602</v>
       </c>
       <c r="Y61" t="s">
-        <v>637</v>
+        <v>646</v>
       </c>
       <c r="Z61" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA61" t="b">
         <v>1</v>
@@ -7233,29 +7286,29 @@
       <c r="H62" t="s">
         <v>186</v>
       </c>
-      <c r="I62">
-        <v>30814593000190</v>
+      <c r="I62" t="s">
+        <v>276</v>
       </c>
       <c r="J62" t="s">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="K62" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L62" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M62" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="O62" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P62" t="s">
-        <v>377</v>
+        <v>276</v>
       </c>
       <c r="Q62" t="s">
-        <v>482</v>
+        <v>491</v>
       </c>
       <c r="R62">
         <v>2018</v>
@@ -7264,25 +7317,25 @@
         <v>8</v>
       </c>
       <c r="T62" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U62">
         <v>2</v>
       </c>
       <c r="V62" t="s">
-        <v>482</v>
+        <v>491</v>
       </c>
       <c r="W62" t="s">
-        <v>561</v>
+        <v>570</v>
       </c>
       <c r="X62" t="s">
-        <v>224</v>
+        <v>329</v>
       </c>
       <c r="Y62" t="s">
-        <v>626</v>
+        <v>635</v>
       </c>
       <c r="Z62" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA62" t="b">
         <v>1</v>
@@ -7313,29 +7366,29 @@
       <c r="H63" t="s">
         <v>187</v>
       </c>
-      <c r="I63">
-        <v>42438349000150</v>
+      <c r="I63" t="s">
+        <v>277</v>
       </c>
       <c r="J63" t="s">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="K63" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L63" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M63" t="s">
-        <v>243</v>
+        <v>348</v>
       </c>
       <c r="O63" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P63" t="s">
-        <v>378</v>
+        <v>277</v>
       </c>
       <c r="Q63" t="s">
-        <v>483</v>
+        <v>492</v>
       </c>
       <c r="R63">
         <v>2021</v>
@@ -7344,25 +7397,25 @@
         <v>5</v>
       </c>
       <c r="T63" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U63">
         <v>2</v>
       </c>
       <c r="V63" t="s">
-        <v>483</v>
+        <v>492</v>
       </c>
       <c r="W63" t="s">
-        <v>562</v>
+        <v>571</v>
       </c>
       <c r="X63" t="s">
-        <v>224</v>
+        <v>329</v>
       </c>
       <c r="Y63" t="s">
-        <v>617</v>
+        <v>626</v>
       </c>
       <c r="Z63" t="s">
-        <v>243</v>
+        <v>348</v>
       </c>
       <c r="AA63" t="b">
         <v>1</v>
@@ -7390,29 +7443,29 @@
       <c r="G64" t="s">
         <v>100</v>
       </c>
-      <c r="I64">
-        <v>19918377000152</v>
+      <c r="I64" t="s">
+        <v>278</v>
       </c>
       <c r="J64" t="s">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="K64" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L64" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M64" t="s">
-        <v>241</v>
+        <v>346</v>
       </c>
       <c r="O64" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P64" t="s">
-        <v>379</v>
+        <v>278</v>
       </c>
       <c r="Q64" t="s">
-        <v>484</v>
+        <v>493</v>
       </c>
       <c r="R64">
         <v>2014</v>
@@ -7421,22 +7474,22 @@
         <v>12</v>
       </c>
       <c r="T64" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U64">
         <v>2</v>
       </c>
       <c r="V64" t="s">
-        <v>484</v>
+        <v>493</v>
       </c>
       <c r="X64" t="s">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="Y64" t="s">
-        <v>638</v>
+        <v>647</v>
       </c>
       <c r="Z64" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA64" t="b">
         <v>1</v>
@@ -7467,32 +7520,32 @@
       <c r="H65" t="s">
         <v>188</v>
       </c>
-      <c r="I65">
-        <v>4545089000122</v>
+      <c r="I65" t="s">
+        <v>279</v>
       </c>
       <c r="J65" t="s">
-        <v>230</v>
+        <v>335</v>
       </c>
       <c r="K65" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L65" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M65" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="N65" t="s">
-        <v>304</v>
+        <v>409</v>
       </c>
       <c r="O65" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P65" t="s">
-        <v>380</v>
+        <v>425</v>
       </c>
       <c r="Q65" t="s">
-        <v>485</v>
+        <v>494</v>
       </c>
       <c r="R65">
         <v>2001</v>
@@ -7501,25 +7554,25 @@
         <v>25</v>
       </c>
       <c r="T65" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U65">
         <v>2</v>
       </c>
       <c r="V65" t="s">
-        <v>533</v>
+        <v>542</v>
       </c>
       <c r="W65" t="s">
-        <v>563</v>
+        <v>572</v>
       </c>
       <c r="X65" t="s">
-        <v>594</v>
+        <v>603</v>
       </c>
       <c r="Y65" t="s">
-        <v>639</v>
+        <v>648</v>
       </c>
       <c r="Z65" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA65" t="b">
         <v>1</v>
@@ -7550,32 +7603,32 @@
       <c r="H66" t="s">
         <v>189</v>
       </c>
-      <c r="I66">
-        <v>39799505000101</v>
+      <c r="I66" t="s">
+        <v>280</v>
       </c>
       <c r="J66" t="s">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="K66" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L66" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M66" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="N66" t="s">
-        <v>305</v>
+        <v>410</v>
       </c>
       <c r="O66" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P66" t="s">
-        <v>381</v>
+        <v>280</v>
       </c>
       <c r="Q66" t="s">
-        <v>486</v>
+        <v>495</v>
       </c>
       <c r="R66">
         <v>2020</v>
@@ -7584,25 +7637,25 @@
         <v>6</v>
       </c>
       <c r="T66" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U66">
         <v>2</v>
       </c>
       <c r="V66" t="s">
-        <v>486</v>
+        <v>495</v>
       </c>
       <c r="W66" t="s">
-        <v>564</v>
+        <v>573</v>
       </c>
       <c r="X66" t="s">
-        <v>224</v>
+        <v>329</v>
       </c>
       <c r="Y66" t="s">
-        <v>640</v>
+        <v>649</v>
       </c>
       <c r="Z66" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA66" t="b">
         <v>1</v>
@@ -7633,32 +7686,32 @@
       <c r="H67" t="s">
         <v>190</v>
       </c>
-      <c r="I67">
-        <v>31191129000158</v>
+      <c r="I67" t="s">
+        <v>281</v>
       </c>
       <c r="J67" t="s">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="K67" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L67" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M67" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="N67" t="s">
-        <v>306</v>
+        <v>411</v>
       </c>
       <c r="O67" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P67" t="s">
-        <v>382</v>
+        <v>281</v>
       </c>
       <c r="Q67" t="s">
-        <v>487</v>
+        <v>496</v>
       </c>
       <c r="R67">
         <v>2018</v>
@@ -7667,25 +7720,25 @@
         <v>8</v>
       </c>
       <c r="T67" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U67">
         <v>2</v>
       </c>
       <c r="V67" t="s">
-        <v>487</v>
+        <v>496</v>
       </c>
       <c r="W67" t="s">
-        <v>565</v>
+        <v>574</v>
       </c>
       <c r="X67" t="s">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="Y67" t="s">
-        <v>611</v>
+        <v>620</v>
       </c>
       <c r="Z67" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA67" t="b">
         <v>1</v>
@@ -7716,32 +7769,32 @@
       <c r="H68" t="s">
         <v>191</v>
       </c>
-      <c r="I68">
-        <v>33233308000136</v>
+      <c r="I68" t="s">
+        <v>282</v>
       </c>
       <c r="J68" t="s">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="K68" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L68" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M68" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="N68" t="s">
-        <v>307</v>
+        <v>412</v>
       </c>
       <c r="O68" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P68" t="s">
-        <v>383</v>
+        <v>282</v>
       </c>
       <c r="Q68" t="s">
-        <v>488</v>
+        <v>497</v>
       </c>
       <c r="R68">
         <v>2019</v>
@@ -7750,25 +7803,25 @@
         <v>7</v>
       </c>
       <c r="T68" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U68">
         <v>2</v>
       </c>
       <c r="V68" t="s">
-        <v>488</v>
+        <v>497</v>
       </c>
       <c r="W68" t="s">
-        <v>566</v>
+        <v>575</v>
       </c>
       <c r="X68" t="s">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="Y68" t="s">
-        <v>600</v>
+        <v>609</v>
       </c>
       <c r="Z68" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA68" t="b">
         <v>1</v>
@@ -7799,32 +7852,32 @@
       <c r="H69" t="s">
         <v>192</v>
       </c>
-      <c r="I69">
-        <v>7216822000668</v>
+      <c r="I69" t="s">
+        <v>283</v>
       </c>
       <c r="J69" t="s">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="K69" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L69" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M69" t="s">
-        <v>243</v>
+        <v>348</v>
       </c>
       <c r="N69" t="s">
-        <v>308</v>
+        <v>413</v>
       </c>
       <c r="O69" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P69" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="Q69" t="s">
-        <v>489</v>
+        <v>498</v>
       </c>
       <c r="R69">
         <v>2017</v>
@@ -7833,25 +7886,25 @@
         <v>9</v>
       </c>
       <c r="T69" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U69">
         <v>2</v>
       </c>
       <c r="V69" t="s">
-        <v>489</v>
+        <v>498</v>
       </c>
       <c r="W69" t="s">
-        <v>567</v>
+        <v>576</v>
       </c>
       <c r="X69" t="s">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="Y69" t="s">
-        <v>641</v>
+        <v>650</v>
       </c>
       <c r="Z69" t="s">
-        <v>243</v>
+        <v>348</v>
       </c>
       <c r="AA69" t="b">
         <v>1</v>
@@ -7882,32 +7935,32 @@
       <c r="H70" t="s">
         <v>193</v>
       </c>
-      <c r="I70">
-        <v>35714405000176</v>
+      <c r="I70" t="s">
+        <v>284</v>
       </c>
       <c r="J70" t="s">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="K70" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L70" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M70" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="N70" t="s">
-        <v>309</v>
+        <v>414</v>
       </c>
       <c r="O70" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P70" t="s">
-        <v>385</v>
+        <v>284</v>
       </c>
       <c r="Q70" t="s">
-        <v>490</v>
+        <v>499</v>
       </c>
       <c r="R70">
         <v>2019</v>
@@ -7916,25 +7969,25 @@
         <v>7</v>
       </c>
       <c r="T70" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U70">
         <v>2</v>
       </c>
       <c r="V70" t="s">
-        <v>490</v>
+        <v>499</v>
       </c>
       <c r="W70" t="s">
-        <v>568</v>
+        <v>577</v>
       </c>
       <c r="X70" t="s">
-        <v>224</v>
+        <v>329</v>
       </c>
       <c r="Y70" t="s">
-        <v>632</v>
+        <v>641</v>
       </c>
       <c r="Z70" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA70" t="b">
         <v>1</v>
@@ -7965,32 +8018,32 @@
       <c r="H71" t="s">
         <v>194</v>
       </c>
-      <c r="I71">
-        <v>33037883000163</v>
+      <c r="I71" t="s">
+        <v>285</v>
       </c>
       <c r="J71" t="s">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="K71" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L71" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M71" t="s">
-        <v>243</v>
+        <v>348</v>
       </c>
       <c r="N71" t="s">
-        <v>310</v>
+        <v>415</v>
       </c>
       <c r="O71" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P71" t="s">
-        <v>386</v>
+        <v>285</v>
       </c>
       <c r="Q71" t="s">
-        <v>491</v>
+        <v>500</v>
       </c>
       <c r="R71">
         <v>2019</v>
@@ -7999,25 +8052,25 @@
         <v>7</v>
       </c>
       <c r="T71" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U71">
         <v>2</v>
       </c>
       <c r="V71" t="s">
-        <v>491</v>
+        <v>500</v>
       </c>
       <c r="W71" t="s">
-        <v>569</v>
+        <v>578</v>
       </c>
       <c r="X71" t="s">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="Y71" t="s">
-        <v>642</v>
+        <v>651</v>
       </c>
       <c r="Z71" t="s">
-        <v>243</v>
+        <v>348</v>
       </c>
       <c r="AA71" t="b">
         <v>1</v>
@@ -8048,32 +8101,32 @@
       <c r="H72" t="s">
         <v>195</v>
       </c>
-      <c r="I72">
-        <v>4419014000103</v>
+      <c r="I72" t="s">
+        <v>286</v>
       </c>
       <c r="J72" t="s">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="K72" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L72" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M72" t="s">
-        <v>243</v>
+        <v>348</v>
       </c>
       <c r="N72" t="s">
-        <v>311</v>
+        <v>416</v>
       </c>
       <c r="O72" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P72" t="s">
-        <v>387</v>
+        <v>427</v>
       </c>
       <c r="Q72" t="s">
-        <v>492</v>
+        <v>501</v>
       </c>
       <c r="R72">
         <v>2001</v>
@@ -8082,25 +8135,25 @@
         <v>25</v>
       </c>
       <c r="T72" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U72">
         <v>2</v>
       </c>
       <c r="V72" t="s">
-        <v>492</v>
+        <v>501</v>
       </c>
       <c r="W72" t="s">
-        <v>570</v>
+        <v>579</v>
       </c>
       <c r="X72" t="s">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="Y72" t="s">
-        <v>643</v>
+        <v>652</v>
       </c>
       <c r="Z72" t="s">
-        <v>243</v>
+        <v>348</v>
       </c>
       <c r="AA72" t="b">
         <v>1</v>
@@ -8131,32 +8184,32 @@
       <c r="H73" t="s">
         <v>196</v>
       </c>
-      <c r="I73">
-        <v>19738868000111</v>
+      <c r="I73" t="s">
+        <v>287</v>
       </c>
       <c r="J73" t="s">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="K73" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L73" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M73" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="N73" t="s">
-        <v>312</v>
+        <v>417</v>
       </c>
       <c r="O73" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P73" t="s">
-        <v>388</v>
+        <v>287</v>
       </c>
       <c r="Q73" t="s">
-        <v>493</v>
+        <v>502</v>
       </c>
       <c r="R73">
         <v>2014</v>
@@ -8165,25 +8218,25 @@
         <v>12</v>
       </c>
       <c r="T73" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U73">
         <v>2</v>
       </c>
       <c r="V73" t="s">
-        <v>493</v>
+        <v>502</v>
       </c>
       <c r="W73" t="s">
-        <v>571</v>
+        <v>580</v>
       </c>
       <c r="X73" t="s">
-        <v>224</v>
+        <v>329</v>
       </c>
       <c r="Y73" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="Z73" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA73" t="b">
         <v>1</v>
@@ -8214,32 +8267,32 @@
       <c r="H74" t="s">
         <v>197</v>
       </c>
-      <c r="I74">
-        <v>57188334000158</v>
+      <c r="I74" t="s">
+        <v>288</v>
       </c>
       <c r="J74" t="s">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="K74" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L74" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M74" t="s">
-        <v>243</v>
+        <v>348</v>
       </c>
       <c r="N74" t="s">
-        <v>313</v>
+        <v>418</v>
       </c>
       <c r="O74" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P74" t="s">
-        <v>389</v>
+        <v>288</v>
       </c>
       <c r="Q74" t="s">
-        <v>494</v>
+        <v>503</v>
       </c>
       <c r="R74">
         <v>2024</v>
@@ -8248,25 +8301,25 @@
         <v>2</v>
       </c>
       <c r="T74" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U74">
         <v>2</v>
       </c>
       <c r="V74" t="s">
-        <v>494</v>
+        <v>503</v>
       </c>
       <c r="W74" t="s">
-        <v>572</v>
+        <v>581</v>
       </c>
       <c r="X74" t="s">
-        <v>224</v>
+        <v>329</v>
       </c>
       <c r="Y74" t="s">
-        <v>640</v>
+        <v>649</v>
       </c>
       <c r="Z74" t="s">
-        <v>243</v>
+        <v>348</v>
       </c>
       <c r="AA74" t="b">
         <v>1</v>
@@ -8297,32 +8350,32 @@
       <c r="H75" t="s">
         <v>198</v>
       </c>
-      <c r="I75">
-        <v>34454171000102</v>
+      <c r="I75" t="s">
+        <v>289</v>
       </c>
       <c r="J75" t="s">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="K75" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L75" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M75" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="N75" t="s">
-        <v>314</v>
+        <v>419</v>
       </c>
       <c r="O75" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P75" t="s">
-        <v>390</v>
+        <v>289</v>
       </c>
       <c r="Q75" t="s">
-        <v>495</v>
+        <v>504</v>
       </c>
       <c r="R75">
         <v>2019</v>
@@ -8331,25 +8384,25 @@
         <v>7</v>
       </c>
       <c r="T75" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U75">
         <v>2</v>
       </c>
       <c r="V75" t="s">
-        <v>495</v>
+        <v>504</v>
       </c>
       <c r="W75" t="s">
-        <v>573</v>
+        <v>582</v>
       </c>
       <c r="X75" t="s">
-        <v>224</v>
+        <v>329</v>
       </c>
       <c r="Y75" t="s">
-        <v>617</v>
+        <v>626</v>
       </c>
       <c r="Z75" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA75" t="b">
         <v>1</v>
@@ -8377,32 +8430,32 @@
       <c r="G76" t="s">
         <v>112</v>
       </c>
-      <c r="I76">
-        <v>33016895000101</v>
+      <c r="I76" t="s">
+        <v>290</v>
       </c>
       <c r="J76" t="s">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="K76" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L76" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M76" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="N76" t="s">
-        <v>315</v>
+        <v>420</v>
       </c>
       <c r="O76" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P76" t="s">
-        <v>391</v>
+        <v>290</v>
       </c>
       <c r="Q76" t="s">
-        <v>496</v>
+        <v>505</v>
       </c>
       <c r="R76">
         <v>2019</v>
@@ -8411,25 +8464,25 @@
         <v>7</v>
       </c>
       <c r="T76" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U76">
         <v>2</v>
       </c>
       <c r="V76" t="s">
-        <v>496</v>
+        <v>505</v>
       </c>
       <c r="W76" t="s">
-        <v>574</v>
+        <v>583</v>
       </c>
       <c r="X76" t="s">
-        <v>224</v>
+        <v>329</v>
       </c>
       <c r="Y76" t="s">
-        <v>644</v>
+        <v>653</v>
       </c>
       <c r="Z76" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA76" t="b">
         <v>1</v>
@@ -8457,32 +8510,32 @@
       <c r="G77" t="s">
         <v>113</v>
       </c>
-      <c r="I77">
-        <v>65731411000100</v>
+      <c r="I77" t="s">
+        <v>291</v>
       </c>
       <c r="J77" t="s">
-        <v>231</v>
+        <v>336</v>
       </c>
       <c r="K77" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L77" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M77" t="s">
-        <v>241</v>
+        <v>346</v>
       </c>
       <c r="N77" t="s">
-        <v>303</v>
+        <v>408</v>
       </c>
       <c r="O77" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P77" t="s">
-        <v>392</v>
+        <v>291</v>
       </c>
       <c r="Q77" t="s">
-        <v>497</v>
+        <v>506</v>
       </c>
       <c r="R77">
         <v>2026</v>
@@ -8491,22 +8544,22 @@
         <v>0</v>
       </c>
       <c r="T77" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U77">
         <v>2</v>
       </c>
       <c r="V77" t="s">
-        <v>497</v>
+        <v>506</v>
       </c>
       <c r="X77" t="s">
-        <v>231</v>
+        <v>336</v>
       </c>
       <c r="Y77" t="s">
-        <v>645</v>
+        <v>654</v>
       </c>
       <c r="Z77" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA77" t="b">
         <v>1</v>
@@ -8534,32 +8587,32 @@
       <c r="G78" t="s">
         <v>114</v>
       </c>
-      <c r="I78">
-        <v>55406246000150</v>
+      <c r="I78" t="s">
+        <v>292</v>
       </c>
       <c r="J78" t="s">
-        <v>231</v>
+        <v>336</v>
       </c>
       <c r="K78" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L78" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M78" t="s">
-        <v>241</v>
+        <v>346</v>
       </c>
       <c r="N78" t="s">
-        <v>303</v>
+        <v>408</v>
       </c>
       <c r="O78" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P78" t="s">
-        <v>393</v>
+        <v>292</v>
       </c>
       <c r="Q78" t="s">
-        <v>498</v>
+        <v>507</v>
       </c>
       <c r="R78">
         <v>2024</v>
@@ -8568,22 +8621,22 @@
         <v>2</v>
       </c>
       <c r="T78" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U78">
         <v>2</v>
       </c>
       <c r="V78" t="s">
-        <v>498</v>
+        <v>507</v>
       </c>
       <c r="X78" t="s">
-        <v>231</v>
+        <v>336</v>
       </c>
       <c r="Y78" t="s">
-        <v>601</v>
+        <v>610</v>
       </c>
       <c r="Z78" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA78" t="b">
         <v>1</v>
@@ -8614,32 +8667,32 @@
       <c r="H79" t="s">
         <v>199</v>
       </c>
-      <c r="I79">
-        <v>7588961000108</v>
+      <c r="I79" t="s">
+        <v>293</v>
       </c>
       <c r="J79" t="s">
-        <v>218</v>
+        <v>323</v>
       </c>
       <c r="K79" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L79" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M79" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="N79" t="s">
-        <v>303</v>
+        <v>408</v>
       </c>
       <c r="O79" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P79" t="s">
-        <v>394</v>
+        <v>428</v>
       </c>
       <c r="Q79" t="s">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="R79">
         <v>2005</v>
@@ -8648,25 +8701,25 @@
         <v>21</v>
       </c>
       <c r="T79" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U79">
         <v>2</v>
       </c>
       <c r="V79" t="s">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="W79" t="s">
-        <v>575</v>
+        <v>584</v>
       </c>
       <c r="X79" t="s">
-        <v>588</v>
+        <v>597</v>
       </c>
       <c r="Y79" t="s">
-        <v>618</v>
+        <v>627</v>
       </c>
       <c r="Z79" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA79" t="b">
         <v>1</v>
@@ -8697,32 +8750,32 @@
       <c r="H80" t="s">
         <v>200</v>
       </c>
-      <c r="I80">
-        <v>22742301000123</v>
+      <c r="I80" t="s">
+        <v>294</v>
       </c>
       <c r="J80" t="s">
-        <v>218</v>
+        <v>323</v>
       </c>
       <c r="K80" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L80" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M80" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="N80" t="s">
-        <v>303</v>
+        <v>408</v>
       </c>
       <c r="O80" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P80" t="s">
-        <v>395</v>
+        <v>294</v>
       </c>
       <c r="Q80" t="s">
-        <v>500</v>
+        <v>509</v>
       </c>
       <c r="R80">
         <v>2015</v>
@@ -8731,22 +8784,22 @@
         <v>11</v>
       </c>
       <c r="T80" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U80">
         <v>2</v>
       </c>
       <c r="V80" t="s">
-        <v>500</v>
+        <v>509</v>
       </c>
       <c r="X80" t="s">
-        <v>588</v>
+        <v>597</v>
       </c>
       <c r="Y80" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="Z80" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA80" t="b">
         <v>1</v>
@@ -8777,32 +8830,32 @@
       <c r="H81" t="s">
         <v>201</v>
       </c>
-      <c r="I81">
-        <v>9415536000142</v>
+      <c r="I81" t="s">
+        <v>295</v>
       </c>
       <c r="J81" t="s">
-        <v>218</v>
+        <v>323</v>
       </c>
       <c r="K81" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L81" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M81" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="N81" t="s">
-        <v>303</v>
+        <v>408</v>
       </c>
       <c r="O81" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P81" t="s">
-        <v>396</v>
+        <v>429</v>
       </c>
       <c r="Q81" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="R81">
         <v>2008</v>
@@ -8811,25 +8864,25 @@
         <v>18</v>
       </c>
       <c r="T81" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U81">
         <v>2</v>
       </c>
       <c r="V81" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="W81" t="s">
-        <v>576</v>
+        <v>585</v>
       </c>
       <c r="X81" t="s">
-        <v>595</v>
+        <v>604</v>
       </c>
       <c r="Y81" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="Z81" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA81" t="b">
         <v>1</v>
@@ -8857,32 +8910,32 @@
       <c r="G82" t="s">
         <v>118</v>
       </c>
-      <c r="I82">
-        <v>64633565000199</v>
+      <c r="I82" t="s">
+        <v>296</v>
       </c>
       <c r="J82" t="s">
-        <v>218</v>
+        <v>323</v>
       </c>
       <c r="K82" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L82" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M82" t="s">
-        <v>241</v>
+        <v>346</v>
       </c>
       <c r="N82" t="s">
-        <v>303</v>
+        <v>408</v>
       </c>
       <c r="O82" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P82" t="s">
-        <v>397</v>
+        <v>296</v>
       </c>
       <c r="Q82" t="s">
-        <v>466</v>
+        <v>475</v>
       </c>
       <c r="R82">
         <v>2026</v>
@@ -8891,22 +8944,22 @@
         <v>0</v>
       </c>
       <c r="T82" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U82">
         <v>2</v>
       </c>
       <c r="V82" t="s">
-        <v>466</v>
+        <v>475</v>
       </c>
       <c r="X82" t="s">
-        <v>588</v>
+        <v>597</v>
       </c>
       <c r="Y82" t="s">
-        <v>614</v>
+        <v>623</v>
       </c>
       <c r="Z82" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA82" t="b">
         <v>1</v>
@@ -8937,32 +8990,32 @@
       <c r="H83" t="s">
         <v>202</v>
       </c>
-      <c r="I83">
-        <v>13744159000162</v>
+      <c r="I83" t="s">
+        <v>297</v>
       </c>
       <c r="J83" t="s">
-        <v>218</v>
+        <v>323</v>
       </c>
       <c r="K83" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L83" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M83" t="s">
-        <v>241</v>
+        <v>346</v>
       </c>
       <c r="N83" t="s">
-        <v>303</v>
+        <v>408</v>
       </c>
       <c r="O83" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P83" t="s">
-        <v>398</v>
+        <v>297</v>
       </c>
       <c r="Q83" t="s">
-        <v>502</v>
+        <v>511</v>
       </c>
       <c r="R83">
         <v>2011</v>
@@ -8971,22 +9024,22 @@
         <v>15</v>
       </c>
       <c r="T83" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U83">
         <v>2</v>
       </c>
       <c r="V83" t="s">
-        <v>502</v>
+        <v>511</v>
       </c>
       <c r="X83" t="s">
-        <v>588</v>
+        <v>597</v>
       </c>
       <c r="Y83" t="s">
-        <v>646</v>
+        <v>655</v>
       </c>
       <c r="Z83" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA83" t="b">
         <v>1</v>
@@ -9017,32 +9070,32 @@
       <c r="H84" t="s">
         <v>203</v>
       </c>
-      <c r="I84">
-        <v>12332167000139</v>
+      <c r="I84" t="s">
+        <v>298</v>
       </c>
       <c r="J84" t="s">
-        <v>218</v>
+        <v>323</v>
       </c>
       <c r="K84" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L84" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M84" t="s">
-        <v>243</v>
+        <v>348</v>
       </c>
       <c r="N84" t="s">
-        <v>303</v>
+        <v>408</v>
       </c>
       <c r="O84" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P84" t="s">
-        <v>399</v>
+        <v>298</v>
       </c>
       <c r="Q84" t="s">
-        <v>503</v>
+        <v>512</v>
       </c>
       <c r="R84">
         <v>2010</v>
@@ -9051,25 +9104,25 @@
         <v>16</v>
       </c>
       <c r="T84" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U84">
         <v>2</v>
       </c>
       <c r="V84" t="s">
-        <v>503</v>
+        <v>512</v>
       </c>
       <c r="W84" t="s">
-        <v>577</v>
+        <v>586</v>
       </c>
       <c r="X84" t="s">
-        <v>588</v>
+        <v>597</v>
       </c>
       <c r="Y84" t="s">
-        <v>611</v>
+        <v>620</v>
       </c>
       <c r="Z84" t="s">
-        <v>243</v>
+        <v>348</v>
       </c>
       <c r="AA84" t="b">
         <v>1</v>
@@ -9097,32 +9150,32 @@
       <c r="G85" t="s">
         <v>121</v>
       </c>
-      <c r="I85">
-        <v>19509749000197</v>
+      <c r="I85" t="s">
+        <v>299</v>
       </c>
       <c r="J85" t="s">
-        <v>218</v>
+        <v>323</v>
       </c>
       <c r="K85" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L85" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M85" t="s">
-        <v>241</v>
+        <v>346</v>
       </c>
       <c r="N85" t="s">
-        <v>303</v>
+        <v>408</v>
       </c>
       <c r="O85" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P85" t="s">
-        <v>400</v>
+        <v>299</v>
       </c>
       <c r="Q85" t="s">
-        <v>504</v>
+        <v>513</v>
       </c>
       <c r="R85">
         <v>2014</v>
@@ -9131,22 +9184,22 @@
         <v>12</v>
       </c>
       <c r="T85" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U85">
         <v>2</v>
       </c>
       <c r="V85" t="s">
-        <v>504</v>
+        <v>513</v>
       </c>
       <c r="X85" t="s">
-        <v>588</v>
+        <v>597</v>
       </c>
       <c r="Y85" t="s">
-        <v>611</v>
+        <v>620</v>
       </c>
       <c r="Z85" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA85" t="b">
         <v>1</v>
@@ -9174,32 +9227,32 @@
       <c r="G86" t="s">
         <v>122</v>
       </c>
-      <c r="I86">
-        <v>61971120000120</v>
+      <c r="I86" t="s">
+        <v>300</v>
       </c>
       <c r="J86" t="s">
-        <v>232</v>
+        <v>337</v>
       </c>
       <c r="K86" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L86" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M86" t="s">
-        <v>241</v>
+        <v>346</v>
       </c>
       <c r="N86" t="s">
-        <v>303</v>
+        <v>408</v>
       </c>
       <c r="O86" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P86" t="s">
-        <v>401</v>
+        <v>300</v>
       </c>
       <c r="Q86" t="s">
-        <v>505</v>
+        <v>514</v>
       </c>
       <c r="R86">
         <v>2025</v>
@@ -9208,22 +9261,22 @@
         <v>1</v>
       </c>
       <c r="T86" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U86">
         <v>2</v>
       </c>
       <c r="V86" t="s">
-        <v>505</v>
+        <v>514</v>
       </c>
       <c r="X86" t="s">
-        <v>596</v>
+        <v>605</v>
       </c>
       <c r="Y86" t="s">
-        <v>647</v>
+        <v>656</v>
       </c>
       <c r="Z86" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA86" t="b">
         <v>1</v>
@@ -9254,32 +9307,32 @@
       <c r="H87" t="s">
         <v>204</v>
       </c>
-      <c r="I87">
-        <v>12643470000152</v>
+      <c r="I87" t="s">
+        <v>301</v>
       </c>
       <c r="J87" t="s">
-        <v>218</v>
+        <v>323</v>
       </c>
       <c r="K87" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L87" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M87" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="N87" t="s">
-        <v>303</v>
+        <v>408</v>
       </c>
       <c r="O87" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P87" t="s">
-        <v>402</v>
+        <v>301</v>
       </c>
       <c r="Q87" t="s">
-        <v>506</v>
+        <v>515</v>
       </c>
       <c r="R87">
         <v>2010</v>
@@ -9288,22 +9341,22 @@
         <v>16</v>
       </c>
       <c r="T87" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U87">
         <v>2</v>
       </c>
       <c r="V87" t="s">
-        <v>506</v>
+        <v>515</v>
       </c>
       <c r="X87" t="s">
-        <v>588</v>
+        <v>597</v>
       </c>
       <c r="Y87" t="s">
-        <v>600</v>
+        <v>609</v>
       </c>
       <c r="Z87" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA87" t="b">
         <v>1</v>
@@ -9331,32 +9384,32 @@
       <c r="G88" t="s">
         <v>124</v>
       </c>
-      <c r="I88">
-        <v>62734248000133</v>
+      <c r="I88" t="s">
+        <v>302</v>
       </c>
       <c r="J88" t="s">
-        <v>233</v>
+        <v>338</v>
       </c>
       <c r="K88" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L88" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M88" t="s">
-        <v>241</v>
+        <v>346</v>
       </c>
       <c r="N88" t="s">
-        <v>303</v>
+        <v>408</v>
       </c>
       <c r="O88" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P88" t="s">
-        <v>403</v>
+        <v>302</v>
       </c>
       <c r="Q88" t="s">
-        <v>507</v>
+        <v>516</v>
       </c>
       <c r="R88">
         <v>2025</v>
@@ -9365,22 +9418,22 @@
         <v>1</v>
       </c>
       <c r="T88" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U88">
         <v>2</v>
       </c>
       <c r="V88" t="s">
-        <v>507</v>
+        <v>516</v>
       </c>
       <c r="X88" t="s">
-        <v>233</v>
+        <v>338</v>
       </c>
       <c r="Y88" t="s">
-        <v>611</v>
+        <v>620</v>
       </c>
       <c r="Z88" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA88" t="b">
         <v>1</v>
@@ -9411,32 +9464,32 @@
       <c r="H89" t="s">
         <v>205</v>
       </c>
-      <c r="I89">
-        <v>27458857000106</v>
+      <c r="I89" t="s">
+        <v>303</v>
       </c>
       <c r="J89" t="s">
-        <v>231</v>
+        <v>336</v>
       </c>
       <c r="K89" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L89" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M89" t="s">
-        <v>241</v>
+        <v>346</v>
       </c>
       <c r="N89" t="s">
+        <v>408</v>
+      </c>
+      <c r="O89" t="s">
+        <v>421</v>
+      </c>
+      <c r="P89" t="s">
         <v>303</v>
       </c>
-      <c r="O89" t="s">
-        <v>316</v>
-      </c>
-      <c r="P89" t="s">
-        <v>404</v>
-      </c>
       <c r="Q89" t="s">
-        <v>508</v>
+        <v>517</v>
       </c>
       <c r="R89">
         <v>2017</v>
@@ -9445,22 +9498,22 @@
         <v>9</v>
       </c>
       <c r="T89" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U89">
         <v>2</v>
       </c>
       <c r="V89" t="s">
-        <v>508</v>
+        <v>517</v>
       </c>
       <c r="X89" t="s">
-        <v>597</v>
+        <v>606</v>
       </c>
       <c r="Y89" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="Z89" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA89" t="b">
         <v>1</v>
@@ -9488,32 +9541,32 @@
       <c r="G90" t="s">
         <v>126</v>
       </c>
-      <c r="I90">
-        <v>58967474000197</v>
+      <c r="I90" t="s">
+        <v>304</v>
       </c>
       <c r="J90" t="s">
-        <v>226</v>
+        <v>331</v>
       </c>
       <c r="K90" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L90" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M90" t="s">
-        <v>241</v>
+        <v>346</v>
       </c>
       <c r="N90" t="s">
-        <v>303</v>
+        <v>408</v>
       </c>
       <c r="O90" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P90" t="s">
-        <v>405</v>
+        <v>304</v>
       </c>
       <c r="Q90" t="s">
-        <v>509</v>
+        <v>518</v>
       </c>
       <c r="R90">
         <v>2025</v>
@@ -9522,22 +9575,22 @@
         <v>1</v>
       </c>
       <c r="T90" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U90">
         <v>2</v>
       </c>
       <c r="V90" t="s">
-        <v>509</v>
+        <v>518</v>
       </c>
       <c r="X90" t="s">
-        <v>226</v>
+        <v>331</v>
       </c>
       <c r="Y90" t="s">
-        <v>602</v>
+        <v>611</v>
       </c>
       <c r="Z90" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA90" t="b">
         <v>1</v>
@@ -9565,32 +9618,32 @@
       <c r="G91" t="s">
         <v>127</v>
       </c>
-      <c r="I91">
-        <v>53637045000138</v>
+      <c r="I91" t="s">
+        <v>305</v>
       </c>
       <c r="J91" t="s">
-        <v>234</v>
+        <v>339</v>
       </c>
       <c r="K91" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L91" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M91" t="s">
-        <v>241</v>
+        <v>346</v>
       </c>
       <c r="N91" t="s">
-        <v>303</v>
+        <v>408</v>
       </c>
       <c r="O91" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P91" t="s">
-        <v>406</v>
+        <v>305</v>
       </c>
       <c r="Q91" t="s">
-        <v>510</v>
+        <v>519</v>
       </c>
       <c r="R91">
         <v>2024</v>
@@ -9599,22 +9652,22 @@
         <v>2</v>
       </c>
       <c r="T91" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U91">
         <v>2</v>
       </c>
       <c r="V91" t="s">
-        <v>510</v>
+        <v>519</v>
       </c>
       <c r="X91" t="s">
-        <v>234</v>
+        <v>339</v>
       </c>
       <c r="Y91" t="s">
-        <v>648</v>
+        <v>657</v>
       </c>
       <c r="Z91" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA91" t="b">
         <v>1</v>
@@ -9642,32 +9695,32 @@
       <c r="G92" t="s">
         <v>128</v>
       </c>
-      <c r="I92">
-        <v>66155958000160</v>
+      <c r="I92" t="s">
+        <v>306</v>
       </c>
       <c r="J92" t="s">
-        <v>235</v>
+        <v>340</v>
       </c>
       <c r="K92" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L92" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M92" t="s">
-        <v>241</v>
+        <v>346</v>
       </c>
       <c r="N92" t="s">
-        <v>303</v>
+        <v>408</v>
       </c>
       <c r="O92" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P92" t="s">
-        <v>407</v>
+        <v>306</v>
       </c>
       <c r="Q92" t="s">
-        <v>511</v>
+        <v>520</v>
       </c>
       <c r="R92">
         <v>2026</v>
@@ -9676,22 +9729,22 @@
         <v>0</v>
       </c>
       <c r="T92" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U92">
         <v>2</v>
       </c>
       <c r="V92" t="s">
-        <v>511</v>
+        <v>520</v>
       </c>
       <c r="X92" t="s">
-        <v>597</v>
+        <v>606</v>
       </c>
       <c r="Y92" t="s">
-        <v>611</v>
+        <v>620</v>
       </c>
       <c r="Z92" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA92" t="b">
         <v>1</v>
@@ -9719,32 +9772,32 @@
       <c r="G93" t="s">
         <v>129</v>
       </c>
-      <c r="I93">
-        <v>56894834000142</v>
+      <c r="I93" t="s">
+        <v>307</v>
       </c>
       <c r="J93" t="s">
-        <v>233</v>
+        <v>338</v>
       </c>
       <c r="K93" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L93" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M93" t="s">
-        <v>241</v>
+        <v>346</v>
       </c>
       <c r="N93" t="s">
-        <v>303</v>
+        <v>408</v>
       </c>
       <c r="O93" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P93" t="s">
-        <v>408</v>
+        <v>307</v>
       </c>
       <c r="Q93" t="s">
-        <v>512</v>
+        <v>521</v>
       </c>
       <c r="R93">
         <v>2024</v>
@@ -9753,22 +9806,22 @@
         <v>2</v>
       </c>
       <c r="T93" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U93">
         <v>2</v>
       </c>
       <c r="V93" t="s">
-        <v>512</v>
+        <v>521</v>
       </c>
       <c r="X93" t="s">
-        <v>233</v>
+        <v>338</v>
       </c>
       <c r="Y93" t="s">
-        <v>617</v>
+        <v>626</v>
       </c>
       <c r="Z93" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA93" t="b">
         <v>1</v>
@@ -9799,32 +9852,32 @@
       <c r="H94" t="s">
         <v>206</v>
       </c>
-      <c r="I94">
-        <v>48856493000192</v>
+      <c r="I94" t="s">
+        <v>308</v>
       </c>
       <c r="J94" t="s">
-        <v>233</v>
+        <v>338</v>
       </c>
       <c r="K94" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L94" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M94" t="s">
-        <v>241</v>
+        <v>346</v>
       </c>
       <c r="N94" t="s">
-        <v>303</v>
+        <v>408</v>
       </c>
       <c r="O94" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P94" t="s">
-        <v>409</v>
+        <v>308</v>
       </c>
       <c r="Q94" t="s">
-        <v>513</v>
+        <v>522</v>
       </c>
       <c r="R94">
         <v>2022</v>
@@ -9833,22 +9886,22 @@
         <v>4</v>
       </c>
       <c r="T94" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U94">
         <v>2</v>
       </c>
       <c r="V94" t="s">
-        <v>513</v>
+        <v>522</v>
       </c>
       <c r="X94" t="s">
-        <v>233</v>
+        <v>338</v>
       </c>
       <c r="Y94" t="s">
-        <v>617</v>
+        <v>626</v>
       </c>
       <c r="Z94" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA94" t="b">
         <v>1</v>
@@ -9876,32 +9929,32 @@
       <c r="G95" t="s">
         <v>131</v>
       </c>
-      <c r="I95">
-        <v>62540238000167</v>
+      <c r="I95" t="s">
+        <v>309</v>
       </c>
       <c r="J95" t="s">
-        <v>233</v>
+        <v>338</v>
       </c>
       <c r="K95" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L95" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M95" t="s">
-        <v>241</v>
+        <v>346</v>
       </c>
       <c r="N95" t="s">
-        <v>303</v>
+        <v>408</v>
       </c>
       <c r="O95" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P95" t="s">
-        <v>410</v>
+        <v>309</v>
       </c>
       <c r="Q95" t="s">
-        <v>514</v>
+        <v>523</v>
       </c>
       <c r="R95">
         <v>2025</v>
@@ -9910,22 +9963,22 @@
         <v>1</v>
       </c>
       <c r="T95" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U95">
         <v>2</v>
       </c>
       <c r="V95" t="s">
-        <v>514</v>
+        <v>523</v>
       </c>
       <c r="X95" t="s">
-        <v>233</v>
+        <v>338</v>
       </c>
       <c r="Y95" t="s">
-        <v>636</v>
+        <v>645</v>
       </c>
       <c r="Z95" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA95" t="b">
         <v>1</v>
@@ -9956,32 +10009,32 @@
       <c r="H96" t="s">
         <v>207</v>
       </c>
-      <c r="I96">
-        <v>19018026000195</v>
+      <c r="I96" t="s">
+        <v>310</v>
       </c>
       <c r="J96" t="s">
-        <v>233</v>
+        <v>338</v>
       </c>
       <c r="K96" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L96" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M96" t="s">
-        <v>241</v>
+        <v>346</v>
       </c>
       <c r="N96" t="s">
-        <v>303</v>
+        <v>408</v>
       </c>
       <c r="O96" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P96" t="s">
-        <v>411</v>
+        <v>310</v>
       </c>
       <c r="Q96" t="s">
-        <v>515</v>
+        <v>524</v>
       </c>
       <c r="R96">
         <v>2013</v>
@@ -9990,22 +10043,22 @@
         <v>13</v>
       </c>
       <c r="T96" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U96">
         <v>2</v>
       </c>
       <c r="V96" t="s">
-        <v>515</v>
+        <v>524</v>
       </c>
       <c r="X96" t="s">
-        <v>233</v>
+        <v>338</v>
       </c>
       <c r="Y96" t="s">
-        <v>611</v>
+        <v>620</v>
       </c>
       <c r="Z96" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA96" t="b">
         <v>1</v>
@@ -10033,32 +10086,32 @@
       <c r="G97" t="s">
         <v>133</v>
       </c>
-      <c r="I97">
-        <v>14415275000109</v>
+      <c r="I97" t="s">
+        <v>311</v>
       </c>
       <c r="J97" t="s">
-        <v>236</v>
+        <v>341</v>
       </c>
       <c r="K97" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L97" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M97" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="N97" t="s">
-        <v>303</v>
+        <v>408</v>
       </c>
       <c r="O97" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P97" t="s">
-        <v>412</v>
+        <v>311</v>
       </c>
       <c r="Q97" t="s">
-        <v>516</v>
+        <v>525</v>
       </c>
       <c r="R97">
         <v>2011</v>
@@ -10067,22 +10120,22 @@
         <v>15</v>
       </c>
       <c r="T97" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U97">
         <v>2</v>
       </c>
       <c r="V97" t="s">
-        <v>516</v>
+        <v>525</v>
       </c>
       <c r="X97" t="s">
-        <v>236</v>
+        <v>341</v>
       </c>
       <c r="Y97" t="s">
-        <v>649</v>
+        <v>658</v>
       </c>
       <c r="Z97" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA97" t="b">
         <v>1</v>
@@ -10113,29 +10166,29 @@
       <c r="H98" t="s">
         <v>208</v>
       </c>
-      <c r="I98">
-        <v>30111864000141</v>
+      <c r="I98" t="s">
+        <v>312</v>
       </c>
       <c r="J98" t="s">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="K98" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L98" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M98" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="O98" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P98" t="s">
-        <v>413</v>
+        <v>312</v>
       </c>
       <c r="Q98" t="s">
-        <v>517</v>
+        <v>526</v>
       </c>
       <c r="R98">
         <v>2018</v>
@@ -10144,25 +10197,25 @@
         <v>8</v>
       </c>
       <c r="T98" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U98">
         <v>2</v>
       </c>
       <c r="V98" t="s">
-        <v>517</v>
+        <v>526</v>
       </c>
       <c r="W98" t="s">
-        <v>578</v>
+        <v>587</v>
       </c>
       <c r="X98" t="s">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="Y98" t="s">
-        <v>617</v>
+        <v>626</v>
       </c>
       <c r="Z98" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA98" t="b">
         <v>1</v>
@@ -10193,29 +10246,29 @@
       <c r="H99" t="s">
         <v>209</v>
       </c>
-      <c r="I99">
-        <v>39861087000127</v>
+      <c r="I99" t="s">
+        <v>313</v>
       </c>
       <c r="J99" t="s">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="K99" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L99" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M99" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="O99" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P99" t="s">
-        <v>414</v>
+        <v>313</v>
       </c>
       <c r="Q99" t="s">
-        <v>518</v>
+        <v>527</v>
       </c>
       <c r="R99">
         <v>2020</v>
@@ -10224,25 +10277,25 @@
         <v>6</v>
       </c>
       <c r="T99" t="s">
+        <v>536</v>
+      </c>
+      <c r="U99">
+        <v>2</v>
+      </c>
+      <c r="V99" t="s">
         <v>527</v>
       </c>
-      <c r="U99">
-        <v>2</v>
-      </c>
-      <c r="V99" t="s">
-        <v>518</v>
-      </c>
       <c r="W99" t="s">
-        <v>579</v>
+        <v>588</v>
       </c>
       <c r="X99" t="s">
-        <v>224</v>
+        <v>329</v>
       </c>
       <c r="Y99" t="s">
-        <v>614</v>
+        <v>623</v>
       </c>
       <c r="Z99" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA99" t="b">
         <v>1</v>
@@ -10273,29 +10326,29 @@
       <c r="H100" t="s">
         <v>210</v>
       </c>
-      <c r="I100">
-        <v>882726000103</v>
+      <c r="I100" t="s">
+        <v>314</v>
       </c>
       <c r="J100" t="s">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="K100" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L100" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M100" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="O100" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P100" t="s">
-        <v>415</v>
+        <v>430</v>
       </c>
       <c r="Q100" t="s">
-        <v>519</v>
+        <v>528</v>
       </c>
       <c r="R100">
         <v>1995</v>
@@ -10304,25 +10357,25 @@
         <v>31</v>
       </c>
       <c r="T100" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U100">
         <v>2</v>
       </c>
       <c r="V100" t="s">
-        <v>535</v>
+        <v>544</v>
       </c>
       <c r="W100" t="s">
-        <v>580</v>
+        <v>589</v>
       </c>
       <c r="X100" t="s">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="Y100" t="s">
-        <v>650</v>
+        <v>659</v>
       </c>
       <c r="Z100" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA100" t="b">
         <v>1</v>
@@ -10353,29 +10406,29 @@
       <c r="H101" t="s">
         <v>211</v>
       </c>
-      <c r="I101">
-        <v>40240878000119</v>
+      <c r="I101" t="s">
+        <v>315</v>
       </c>
       <c r="J101" t="s">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="K101" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L101" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M101" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="O101" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P101" t="s">
-        <v>416</v>
+        <v>315</v>
       </c>
       <c r="Q101" t="s">
-        <v>520</v>
+        <v>529</v>
       </c>
       <c r="R101">
         <v>2021</v>
@@ -10384,25 +10437,25 @@
         <v>5</v>
       </c>
       <c r="T101" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U101">
         <v>2</v>
       </c>
       <c r="V101" t="s">
-        <v>520</v>
+        <v>529</v>
       </c>
       <c r="W101" t="s">
-        <v>581</v>
+        <v>590</v>
       </c>
       <c r="X101" t="s">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="Y101" t="s">
-        <v>651</v>
+        <v>660</v>
       </c>
       <c r="Z101" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA101" t="b">
         <v>1</v>
@@ -10433,29 +10486,29 @@
       <c r="H102" t="s">
         <v>212</v>
       </c>
-      <c r="I102">
-        <v>24344687000140</v>
+      <c r="I102" t="s">
+        <v>316</v>
       </c>
       <c r="J102" t="s">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="K102" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L102" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M102" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="O102" t="s">
+        <v>421</v>
+      </c>
+      <c r="P102" t="s">
         <v>316</v>
       </c>
-      <c r="P102" t="s">
-        <v>417</v>
-      </c>
       <c r="Q102" t="s">
-        <v>521</v>
+        <v>530</v>
       </c>
       <c r="R102">
         <v>2016</v>
@@ -10464,25 +10517,25 @@
         <v>10</v>
       </c>
       <c r="T102" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U102">
         <v>2</v>
       </c>
       <c r="V102" t="s">
-        <v>521</v>
+        <v>530</v>
       </c>
       <c r="W102" t="s">
-        <v>582</v>
+        <v>591</v>
       </c>
       <c r="X102" t="s">
-        <v>224</v>
+        <v>329</v>
       </c>
       <c r="Y102" t="s">
-        <v>611</v>
+        <v>620</v>
       </c>
       <c r="Z102" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA102" t="b">
         <v>1</v>
@@ -10513,29 +10566,29 @@
       <c r="H103" t="s">
         <v>213</v>
       </c>
-      <c r="I103">
-        <v>10625190000196</v>
+      <c r="I103" t="s">
+        <v>317</v>
       </c>
       <c r="J103" t="s">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="K103" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L103" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M103" t="s">
-        <v>243</v>
+        <v>348</v>
       </c>
       <c r="O103" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P103" t="s">
-        <v>418</v>
+        <v>317</v>
       </c>
       <c r="Q103" t="s">
-        <v>522</v>
+        <v>531</v>
       </c>
       <c r="R103">
         <v>2009</v>
@@ -10544,25 +10597,25 @@
         <v>17</v>
       </c>
       <c r="T103" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U103">
         <v>2</v>
       </c>
       <c r="V103" t="s">
-        <v>522</v>
+        <v>531</v>
       </c>
       <c r="W103" t="s">
-        <v>583</v>
+        <v>592</v>
       </c>
       <c r="X103" t="s">
-        <v>224</v>
+        <v>329</v>
       </c>
       <c r="Y103" t="s">
-        <v>622</v>
+        <v>631</v>
       </c>
       <c r="Z103" t="s">
-        <v>243</v>
+        <v>348</v>
       </c>
       <c r="AA103" t="b">
         <v>1</v>
@@ -10593,29 +10646,29 @@
       <c r="H104" t="s">
         <v>214</v>
       </c>
-      <c r="I104">
-        <v>37016656000102</v>
+      <c r="I104" t="s">
+        <v>318</v>
       </c>
       <c r="J104" t="s">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="K104" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L104" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M104" t="s">
-        <v>243</v>
+        <v>348</v>
       </c>
       <c r="O104" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P104" t="s">
-        <v>419</v>
+        <v>318</v>
       </c>
       <c r="Q104" t="s">
-        <v>523</v>
+        <v>532</v>
       </c>
       <c r="R104">
         <v>1991</v>
@@ -10624,25 +10677,25 @@
         <v>35</v>
       </c>
       <c r="T104" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U104">
         <v>2</v>
       </c>
       <c r="V104" t="s">
-        <v>536</v>
+        <v>545</v>
       </c>
       <c r="W104" t="s">
-        <v>584</v>
+        <v>593</v>
       </c>
       <c r="X104" t="s">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="Y104" t="s">
-        <v>605</v>
+        <v>614</v>
       </c>
       <c r="Z104" t="s">
-        <v>243</v>
+        <v>348</v>
       </c>
       <c r="AA104" t="b">
         <v>1</v>
@@ -10673,29 +10726,29 @@
       <c r="H105" t="s">
         <v>215</v>
       </c>
-      <c r="I105">
-        <v>30348035000187</v>
+      <c r="I105" t="s">
+        <v>319</v>
       </c>
       <c r="J105" t="s">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="K105" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L105" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M105" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="O105" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P105" t="s">
-        <v>420</v>
+        <v>319</v>
       </c>
       <c r="Q105" t="s">
-        <v>524</v>
+        <v>533</v>
       </c>
       <c r="R105">
         <v>2018</v>
@@ -10704,25 +10757,25 @@
         <v>8</v>
       </c>
       <c r="T105" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U105">
         <v>2</v>
       </c>
       <c r="V105" t="s">
-        <v>524</v>
+        <v>533</v>
       </c>
       <c r="W105" t="s">
-        <v>585</v>
+        <v>594</v>
       </c>
       <c r="X105" t="s">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="Y105" t="s">
-        <v>652</v>
+        <v>661</v>
       </c>
       <c r="Z105" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA105" t="b">
         <v>1</v>
@@ -10753,29 +10806,29 @@
       <c r="H106" t="s">
         <v>214</v>
       </c>
-      <c r="I106">
-        <v>18053359000192</v>
+      <c r="I106" t="s">
+        <v>320</v>
       </c>
       <c r="J106" t="s">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="K106" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
       <c r="L106" t="s">
-        <v>240</v>
+        <v>345</v>
       </c>
       <c r="M106" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="O106" t="s">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="P106" t="s">
-        <v>421</v>
+        <v>320</v>
       </c>
       <c r="Q106" t="s">
-        <v>525</v>
+        <v>534</v>
       </c>
       <c r="R106">
         <v>2013</v>
@@ -10784,25 +10837,25 @@
         <v>13</v>
       </c>
       <c r="T106" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="U106">
         <v>2</v>
       </c>
       <c r="V106" t="s">
-        <v>525</v>
+        <v>534</v>
       </c>
       <c r="W106" t="s">
-        <v>586</v>
+        <v>595</v>
       </c>
       <c r="X106" t="s">
-        <v>598</v>
+        <v>607</v>
       </c>
       <c r="Y106" t="s">
-        <v>608</v>
+        <v>617</v>
       </c>
       <c r="Z106" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="AA106" t="b">
         <v>1</v>
